--- a/BIS_usa.xlsx
+++ b/BIS_usa.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>62.7</v>
+        <v>63.7</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -588,14 +588,14 @@
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>36.3</v>
+        <v>38.7</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -604,10 +604,10 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>53.6</v>
+        <v>66.7</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>39.3</v>
+        <v>42.4</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -638,25 +638,25 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>43.2</v>
+        <v>44.8</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>41.7</v>
+        <v>47.9</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -665,21 +665,21 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>36.8</v>
+        <v>42.2</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>47.4</v>
+        <v>50.6</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4">
@@ -690,7 +690,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -699,25 +699,25 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>59.3</v>
+        <v>47.6</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>45.7</v>
+        <v>40.2</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -726,21 +726,21 @@
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>62.1</v>
+        <v>45.5</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>48.3</v>
+        <v>51.5</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -751,19 +751,19 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>35.3</v>
+        <v>46.3</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>139</v>
+        <v>67</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -771,37 +771,37 @@
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>46</v>
+        <v>41.8</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>139</v>
+        <v>67</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>46.9</v>
+        <v>50</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -812,7 +812,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -821,37 +821,37 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>43.4</v>
+        <v>54.1</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>42.6</v>
+        <v>40.5</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>42.9</v>
+        <v>65.2</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>46.9</v>
+        <v>56.5</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -873,7 +873,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -882,25 +882,25 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>50.7</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>44.3</v>
+        <v>35.6</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>76.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>44.7</v>
+        <v>39.3</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -934,7 +934,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>50.5</v>
+        <v>57.8</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -954,14 +954,14 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>41.4</v>
+        <v>39.8</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -970,21 +970,21 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>56.5</v>
+        <v>58.1</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>43.5</v>
+        <v>51.6</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -995,7 +995,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>46</v>
+        <v>43.5</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1015,26 +1015,26 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>43.5</v>
+        <v>39.8</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>45.8</v>
+        <v>37.2</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>43.8</v>
+        <v>44.2</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1065,25 +1065,25 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>56.4</v>
+        <v>53.4</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>43.6</v>
+        <v>37.9</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>47.4</v>
+        <v>58.3</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>52.6</v>
+        <v>45.8</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1126,10 +1126,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>53.9</v>
+        <v>48.4</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1137,14 +1137,14 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>39.3</v>
+        <v>39.8</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>50</v>
+        <v>45.7</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
@@ -1164,10 +1164,10 @@
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>43.3</v>
+        <v>45.7</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>59.1</v>
+        <v>42.1</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1198,14 +1198,14 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>36.4</v>
+        <v>45.8</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>75.90000000000001</v>
+        <v>54.8</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>41.4</v>
+        <v>38.7</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1248,48 +1248,48 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>61.4</v>
+        <v>66.2</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>D-N-D-U</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>D-D-N-D</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N13" s="3" t="n">
-        <v>43.3</v>
+        <v>41.4</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1309,25 +1309,25 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>59.4</v>
+        <v>52.6</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>36.5</v>
+        <v>38.9</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-U</t>
+          <t>U-N-U-U</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1336,21 +1336,21 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>59.5</v>
+        <v>43.8</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>37.8</v>
+        <v>40.6</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>59.6</v>
+        <v>57.1</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>42.4</v>
+        <v>42.9</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1397,21 +1397,21 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>69</v>
+        <v>64.3</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>37.9</v>
+        <v>40.5</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>39.5</v>
+        <v>44.8</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1442,26 +1442,26 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>40.1</v>
+        <v>37.3</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>35.7</v>
+        <v>47.2</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>42.9</v>
+        <v>37.7</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1492,25 +1492,25 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>75.59999999999999</v>
+        <v>61</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>37.8</v>
+        <v>45.8</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1519,21 +1519,21 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>76.5</v>
+        <v>46.7</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>47.1</v>
+        <v>40</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1553,10 +1553,10 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>46.6</v>
+        <v>43.9</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1564,26 +1564,26 @@
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>43.8</v>
+        <v>47</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>42.3</v>
+        <v>36.7</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1614,25 +1614,25 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>46.2</v>
+        <v>56.1</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>41.5</v>
+        <v>34.5</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1641,21 +1641,21 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>47.2</v>
+        <v>57.4</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>36.1</v>
+        <v>35.2</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1675,48 +1675,48 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>40.3</v>
+        <v>40</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>40.3</v>
+        <v>44.3</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>53.3</v>
+        <v>36</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>36.7</v>
+        <v>50</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1736,10 +1736,10 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>35.1</v>
+        <v>43.9</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1747,14 +1747,14 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>43.9</v>
+        <v>43.4</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>39.3</v>
+        <v>50.8</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>47.5</v>
+        <v>50.8</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1797,25 +1797,25 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>54.1</v>
+        <v>53</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>43.1</v>
+        <v>41.9</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1824,21 +1824,21 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>44.7</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>41.7</v>
+        <v>40.4</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1858,48 +1858,48 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>36.9</v>
+        <v>35.8</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>39.4</v>
+        <v>40.9</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>35.9</v>
+        <v>38.1</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N23" s="3" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>74.8</v>
+        <v>81.8</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1930,14 +1930,14 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>48.1</v>
+        <v>44.8</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1946,10 +1946,10 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>56.2</v>
+        <v>45</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>63.5</v>
+        <v>55.4</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1991,14 +1991,14 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>41.3</v>
+        <v>40.5</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>104</v>
+        <v>74</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2007,18 +2007,18 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>54.2</v>
+        <v>62.5</v>
       </c>
       <c r="L25" s="4" t="n">
         <v>24</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="O25" s="4" t="n">
         <v>24</v>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2041,48 +2041,48 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>D-D-N-N</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="L26" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="n">
         <v>48.1</v>
       </c>
-      <c r="E26" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>81</v>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-N</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n">
-        <v>36</v>
-      </c>
       <c r="O26" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -2113,14 +2113,14 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>46.5</v>
+        <v>44</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-U</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>83.3</v>
+        <v>72.7</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>61.1</v>
+        <v>40.9</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2163,25 +2163,25 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>56.3</v>
+        <v>63.9</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>42.5</v>
+        <v>40.2</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2190,21 +2190,21 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>48.1</v>
+        <v>56.8</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>44.4</v>
+        <v>40.5</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>74.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -2235,14 +2235,14 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>39</v>
+        <v>38.5</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>43.2</v>
+        <v>47</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2296,14 +2296,14 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>40.9</v>
+        <v>39.1</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>43.8</v>
+        <v>44.4</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>45.8</v>
+        <v>42.6</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31">
@@ -2337,19 +2337,19 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>44.7</v>
+        <v>36.4</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2357,34 +2357,34 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>50</v>
+        <v>43.6</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>52.4</v>
+        <v>57.1</v>
       </c>
       <c r="L31" s="4" t="n">
         <v>21</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>33.3</v>
       </c>
       <c r="O31" s="4" t="n">
         <v>21</v>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>67</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2418,14 +2418,14 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>46.2</v>
+        <v>38.4</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>56.2</v>
+        <v>85.2</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>43.8</v>
+        <v>51.9</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2468,25 +2468,25 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>38.9</v>
+        <v>47.7</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>167</v>
+        <v>44</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>42.5</v>
+        <v>54.5</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>167</v>
+        <v>44</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2495,21 +2495,21 @@
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>40.8</v>
+        <v>59.1</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N33" s="3" t="n">
-        <v>44.7</v>
+        <v>59.1</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>76</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>54.8</v>
+        <v>53.9</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2540,14 +2540,14 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>35.7</v>
+        <v>39.3</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>50</v>
+        <v>60.7</v>
       </c>
       <c r="L34" s="4" t="n">
         <v>28</v>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2590,25 +2590,25 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>46.5</v>
+        <v>50.6</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>44.6</v>
+        <v>39.3</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2617,21 +2617,21 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>44.4</v>
+        <v>51.4</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>58.3</v>
+        <v>40.5</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36">
@@ -2642,19 +2642,19 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>46.3</v>
+        <v>37.5</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2662,37 +2662,37 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>53.7</v>
+        <v>50</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>60</v>
+        <v>53.3</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>41</v>
+        <v>40.6</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2723,14 +2723,14 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>41.9</v>
+        <v>41.5</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -2739,21 +2739,21 @@
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>35.1</v>
+        <v>40</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>45.9</v>
+        <v>47.5</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2773,25 +2773,25 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>53.2</v>
+        <v>62.7</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>38.7</v>
+        <v>34.3</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2800,21 +2800,21 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>43.5</v>
+        <v>58.3</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>39.1</v>
+        <v>37.5</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2834,10 +2834,10 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>76.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>118</v>
+        <v>254</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2845,14 +2845,14 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>44.9</v>
+        <v>50</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>118</v>
+        <v>254</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>71</v>
+        <v>86.8</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>45.2</v>
+        <v>39.6</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40">
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2906,14 +2906,14 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>82.90000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>41.5</v>
+        <v>50.6</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>41</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41">
@@ -2947,19 +2947,19 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>54.5</v>
+        <v>40.4</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>11</v>
+        <v>141</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2967,26 +2967,26 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>81.8</v>
+        <v>43.3</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>11</v>
+        <v>141</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>75</v>
+        <v>45.5</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>50</v>
+        <v>40.9</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3017,25 +3017,25 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>48.9</v>
+        <v>47</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>35.6</v>
+        <v>41</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-U</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>53.3</v>
+        <v>46.9</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>36.7</v>
+        <v>43.8</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3078,25 +3078,25 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>46.3</v>
+        <v>43.2</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>38.9</v>
+        <v>40.9</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3105,21 +3105,21 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>45</v>
+        <v>52.4</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>50</v>
+        <v>38.1</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44">
@@ -3130,34 +3130,34 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>37.5</v>
+        <v>40.6</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>47.3</v>
+        <v>44.6</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3166,21 +3166,21 @@
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>38.4</v>
+        <v>39.1</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>45.2</v>
+        <v>50.6</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>73</v>
+        <v>87</v>
       </c>
     </row>
     <row r="45">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>65.5</v>
+        <v>57</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -3211,14 +3211,14 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>44</v>
+        <v>40.7</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>76</v>
+        <v>57.7</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>44</v>
+        <v>34.6</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46">
@@ -3252,57 +3252,57 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="E46" s="4" t="n">
+        <v>186</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>186</v>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>N-D-U-D</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="L46" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>U-N-D-N</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N46" s="3" t="n">
         <v>60</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3322,48 +3322,48 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>39.5</v>
+        <v>37.2</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>47.6</v>
+        <v>45.9</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>35.1</v>
+        <v>44.3</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>43.9</v>
+        <v>50</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
     </row>
     <row r="48">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>58.2</v>
+        <v>55.4</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -3394,14 +3394,14 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>38</v>
+        <v>37.6</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3410,21 +3410,21 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>43.3</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>44.1</v>
+        <v>36.7</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>67.7</v>
+        <v>72.8</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3455,14 +3455,14 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>47.2</v>
+        <v>50</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>60.7</v>
+        <v>75.8</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>57.1</v>
+        <v>57.6</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3505,25 +3505,25 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>71.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>38.5</v>
+        <v>50</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3532,21 +3532,21 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>61.9</v>
+        <v>73.3</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>52.4</v>
+        <v>46.7</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>46.1</v>
+        <v>51.9</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3577,26 +3577,26 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>42.7</v>
+        <v>44.2</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>47.1</v>
+        <v>37.5</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
@@ -3604,10 +3604,10 @@
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>47.1</v>
+        <v>45</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="52">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3627,25 +3627,25 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>46.9</v>
+        <v>48.8</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>37.2</v>
+        <v>39.5</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3654,21 +3654,21 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>51.1</v>
+        <v>40.5</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>40</v>
+        <v>45.2</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>73.8</v>
+        <v>82</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3699,14 +3699,14 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>39.2</v>
+        <v>40</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3715,10 +3715,10 @@
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
@@ -3726,10 +3726,10 @@
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>41</v>
+        <v>42.6</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="54">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3749,25 +3749,25 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>44.1</v>
+        <v>59.8</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>44.9</v>
+        <v>37.8</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-N-N</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -3776,10 +3776,10 @@
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>45</v>
+        <v>46.7</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3810,48 +3810,48 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>53.7</v>
+        <v>37.8</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>37</v>
+        <v>37.8</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>56.8</v>
+        <v>36.7</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>37.8</v>
+        <v>46.7</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -4027,17 +4027,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -4046,48 +4046,48 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>60</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>53.3</v>
+        <v>40.7</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M2" s="3" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -4098,17 +4098,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -4117,48 +4117,48 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>45.2</v>
+        <v>46.4</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>45.2</v>
+        <v>35.7</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>43.8</v>
+        <v>40</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -4169,64 +4169,64 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
         <v>57.1</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>2</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q4" s="4" t="n">
         <v>2</v>
@@ -4240,29 +4240,29 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>56</v>
+        <v>42.9</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -4270,26 +4270,26 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>48</v>
+        <v>57.1</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>58.3</v>
+        <v>75</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>41.7</v>
+        <v>75</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -4311,17 +4311,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -4330,37 +4330,37 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>D-D-U-N</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-U</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>44.4</v>
-      </c>
       <c r="N6" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>44.4</v>
+        <v>100</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -4401,25 +4401,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>37.5</v>
-      </c>
       <c r="J7" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -4428,21 +4428,21 @@
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -4453,17 +4453,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -4472,41 +4472,41 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>41.4</v>
+        <v>50</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>51.7</v>
+        <v>50</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M8" s="3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>5</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
@@ -4524,17 +4524,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -4543,37 +4543,37 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>56</v>
+        <v>57.9</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>40</v>
+        <v>42.1</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>37.5</v>
+        <v>55.6</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>62.5</v>
+        <v>55.6</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -4595,67 +4595,67 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>41.7</v>
+        <v>58.3</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>12</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -4666,17 +4666,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -4685,48 +4685,48 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>53.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>66.7</v>
+        <v>85.7</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>33.3</v>
+        <v>57.1</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -4737,17 +4737,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>52.9</v>
+        <v>55.6</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -4767,14 +4767,14 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>58.8</v>
+        <v>72.2</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -4808,17 +4808,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -4827,48 +4827,48 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>60</v>
+        <v>83.3</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>46.7</v>
+        <v>58.3</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-D</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M13" s="3" t="n">
         <v>100</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -4879,17 +4879,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -4898,37 +4898,37 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>40.9</v>
+        <v>61.9</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>36.4</v>
+        <v>47.6</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-U</t>
+          <t>U-N-U-U</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>36.4</v>
+        <v>62.5</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>45.5</v>
+        <v>62.5</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -4950,17 +4950,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>58.3</v>
+        <v>56.2</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
@@ -4980,37 +4980,37 @@
         </is>
       </c>
       <c r="I15" s="3" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-U</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J15" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>N-D-U-U</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="N15" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="M15" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="P15" s="3" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -5021,44 +5021,44 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>38.1</v>
+        <v>41.7</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>33.3</v>
+        <v>41.7</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -5078,10 +5078,10 @@
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>50</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -5092,17 +5092,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -5114,7 +5114,7 @@
         <v>50</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -5125,16 +5125,16 @@
         <v>50</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M17" s="3" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
@@ -5163,29 +5163,29 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>41.7</v>
+        <v>40</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -5196,34 +5196,34 @@
         <v>50</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M18" s="3" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -5234,17 +5234,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -5253,25 +5253,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="G19" s="4" t="n">
         <v>25</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -5280,21 +5280,21 @@
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>55.6</v>
+        <v>80</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -5305,29 +5305,29 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>52.2</v>
+        <v>43.8</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -5335,14 +5335,14 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>52.2</v>
+        <v>50</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5351,21 +5351,21 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -5376,67 +5376,67 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-D</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="N21" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-D</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="N21" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="P21" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -5447,17 +5447,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -5466,25 +5466,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>60</v>
+        <v>55.6</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -5493,21 +5493,21 @@
         </is>
       </c>
       <c r="M22" s="3" t="n">
-        <v>83.3</v>
+        <v>57.1</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>58.3</v>
+        <v>35.7</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -5518,67 +5518,67 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-D</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="n">
         <v>45.5</v>
       </c>
-      <c r="G23" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>U-U-D-U</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>61.5</v>
-      </c>
       <c r="N23" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
-        <v>38.5</v>
+        <v>45.5</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -5589,17 +5589,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -5608,25 +5608,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>87.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>83.3</v>
+        <v>41.2</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -5638,18 +5638,18 @@
         <v>100</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -5660,67 +5660,67 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>45.5</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>47.8</v>
+        <v>54.5</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M25" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
-        <v>42.9</v>
+        <v>75</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -5731,29 +5731,29 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>41.7</v>
+        <v>81.8</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -5761,14 +5761,14 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>58.3</v>
+        <v>45.5</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -5777,10 +5777,10 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -5802,17 +5802,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -5821,48 +5821,48 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>64.3</v>
+        <v>56.2</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>57.1</v>
+        <v>37.5</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-U</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -5873,17 +5873,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -5892,37 +5892,37 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>53.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>69.2</v>
+        <v>38.1</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -5944,17 +5944,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -5963,25 +5963,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>81.8</v>
+        <v>68.2</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>63.6</v>
+        <v>40.9</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -5990,21 +5990,21 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -6015,17 +6015,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -6034,25 +6034,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>64.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>47.1</v>
+        <v>38.5</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -6061,21 +6061,21 @@
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>50</v>
+        <v>77.8</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -6086,29 +6086,29 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>72.7</v>
+        <v>35.3</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -6116,14 +6116,14 @@
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>63.6</v>
+        <v>47.1</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -6132,21 +6132,21 @@
         </is>
       </c>
       <c r="M31" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P31" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -6157,17 +6157,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -6176,25 +6176,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>84.2</v>
+        <v>77.8</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>57.9</v>
+        <v>38.9</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -6203,21 +6203,21 @@
         </is>
       </c>
       <c r="M32" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N32" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="N32" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="Q32" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -6228,67 +6228,67 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>41.5</v>
+        <v>54.5</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>51.2</v>
+        <v>45.5</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>41</v>
+        <v>11</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M33" s="3" t="n">
-        <v>42.9</v>
+        <v>75</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P33" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -6299,17 +6299,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -6318,10 +6318,10 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>66.7</v>
+        <v>61.1</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -6329,14 +6329,14 @@
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -6352,11 +6352,11 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P34" s="3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q34" s="4" t="n">
         <v>5</v>
@@ -6370,17 +6370,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -6389,25 +6389,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>63.6</v>
+        <v>52.4</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>45.5</v>
+        <v>33.3</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
         </is>
       </c>
       <c r="M35" s="3" t="n">
-        <v>66.7</v>
+        <v>44.4</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>9</v>
@@ -6427,7 +6427,7 @@
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>66.7</v>
+        <v>44.4</v>
       </c>
       <c r="Q35" s="4" t="n">
         <v>9</v>
@@ -6441,29 +6441,29 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>80</v>
+        <v>57.1</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -6471,14 +6471,14 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>80</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -6490,18 +6490,18 @@
         <v>100</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P36" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -6527,52 +6527,52 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>47.1</v>
+        <v>44.4</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>41.2</v>
+        <v>44.4</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M37" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P37" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
@@ -6583,67 +6583,67 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>47.1</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>64.7</v>
+        <v>36.8</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M38" s="3" t="n">
-        <v>37.5</v>
+        <v>60</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P38" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39">
@@ -6654,17 +6654,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>75</v>
+        <v>72.5</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -6684,37 +6684,37 @@
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>60.7</v>
+        <v>43.1</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>42.9</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P39" s="3" t="n">
-        <v>57.1</v>
+        <v>41.2</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="M40" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -6782,10 +6782,10 @@
         </is>
       </c>
       <c r="P40" s="3" t="n">
-        <v>38.5</v>
+        <v>63.2</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
@@ -6796,29 +6796,29 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>66.7</v>
+        <v>44.4</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -6826,14 +6826,14 @@
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>100</v>
+        <v>48.1</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="M41" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="P41" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -6867,56 +6867,56 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>53.3</v>
+        <v>33.3</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>66.7</v>
+        <v>41.7</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-U</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M42" s="3" t="n">
-        <v>83.3</v>
+        <v>33.3</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>66.7</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -6938,17 +6938,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -6957,10 +6957,10 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>61.5</v>
+        <v>56.2</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -6968,37 +6968,37 @@
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>46.2</v>
+        <v>37.5</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M43" s="3" t="n">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P43" s="3" t="n">
-        <v>66.7</v>
+        <v>33.3</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -7009,56 +7009,56 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>54.5</v>
+        <v>53.1</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>54.5</v>
+        <v>46.9</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M44" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -7066,10 +7066,10 @@
         </is>
       </c>
       <c r="P44" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45">
@@ -7080,17 +7080,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>63.6</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -7110,37 +7110,37 @@
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>54.5</v>
+        <v>50</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="N45" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
           <t>D/N</t>
         </is>
       </c>
-      <c r="M45" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N45" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="P45" s="3" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
@@ -7151,49 +7151,49 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>50</v>
+        <v>51.5</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>N-D-U-D</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
           <t>D/U</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>U-N-D-N</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
         </is>
       </c>
       <c r="M46" s="3" t="n">
@@ -7204,11 +7204,11 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q46" s="4" t="n">
         <v>2</v>
@@ -7222,29 +7222,29 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -7252,37 +7252,37 @@
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
@@ -7293,17 +7293,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -7312,25 +7312,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>41.2</v>
+        <v>66.7</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>41.2</v>
+        <v>44.4</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -7339,21 +7339,21 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>44.4</v>
+        <v>57.1</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>55.6</v>
+        <v>42.9</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49">
@@ -7364,17 +7364,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -7383,10 +7383,10 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>57.1</v>
+        <v>70.8</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
@@ -7394,14 +7394,14 @@
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>52.4</v>
+        <v>62.5</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -7410,7 +7410,7 @@
         </is>
       </c>
       <c r="M49" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="N49" s="4" t="n">
         <v>7</v>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="P49" s="3" t="n">
-        <v>57.1</v>
+        <v>85.7</v>
       </c>
       <c r="Q49" s="4" t="n">
         <v>7</v>
@@ -7435,17 +7435,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -7454,25 +7454,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>42.9</v>
+        <v>45</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -7481,21 +7481,21 @@
         </is>
       </c>
       <c r="M50" s="3" t="n">
-        <v>50</v>
+        <v>87.5</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P50" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
@@ -7506,56 +7506,56 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>55.6</v>
+        <v>76.5</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>33.3</v>
+        <v>47.1</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M51" s="3" t="n">
         <v>66.7</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -7563,10 +7563,10 @@
         </is>
       </c>
       <c r="P51" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
@@ -7577,67 +7577,67 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>40</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>U-N-U-D</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>33.3</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
@@ -7648,17 +7648,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>91.3</v>
+        <v>81</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -7678,14 +7678,14 @@
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>43.5</v>
+        <v>47.6</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -7694,10 +7694,10 @@
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
@@ -7705,10 +7705,10 @@
         </is>
       </c>
       <c r="P53" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54">
@@ -7719,17 +7719,17 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -7738,10 +7738,10 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>44.8</v>
+        <v>40</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -7749,14 +7749,14 @@
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>37.9</v>
+        <v>53.3</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-N-N</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -7765,10 +7765,10 @@
         </is>
       </c>
       <c r="M54" s="3" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>33.3</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -7790,29 +7790,29 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Cuma</t>
+          <t>Pazartesi</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>50</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -7820,37 +7820,37 @@
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>47.1</v>
+        <v>50</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M55" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P55" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/BIS_usa.xlsx
+++ b/BIS_usa.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -577,25 +577,25 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>63.7</v>
+        <v>40.4</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>38.7</v>
+        <v>39.4</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-U</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -604,21 +604,21 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>66.7</v>
+        <v>37.5</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>42.4</v>
+        <v>39.6</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -638,25 +638,25 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44.8</v>
+        <v>43</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>47.9</v>
+        <v>42</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>42.2</v>
+        <v>48.9</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>50.6</v>
+        <v>43.5</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4">
@@ -690,7 +690,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -699,25 +699,25 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>47.6</v>
+        <v>38.6</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>40.2</v>
+        <v>45.7</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>82</v>
+        <v>127</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-D</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
@@ -751,34 +751,34 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>46.3</v>
+        <v>38.9</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>41.8</v>
+        <v>48.6</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-D</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -787,10 +787,10 @@
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>50</v>
+        <v>46.4</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>50</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -812,7 +812,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -821,25 +821,25 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>54.1</v>
+        <v>59.1</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>40.5</v>
+        <v>51.5</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>65.2</v>
+        <v>50</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>56.5</v>
+        <v>50</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -873,7 +873,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -882,25 +882,25 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>50.7</v>
+        <v>44.3</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>35.6</v>
+        <v>34.1</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-D</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -909,21 +909,21 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>45.5</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>39.3</v>
+        <v>63.6</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -934,7 +934,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -943,25 +943,25 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>57.8</v>
+        <v>43.8</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-D</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -970,21 +970,21 @@
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>58.1</v>
+        <v>48.1</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>51.6</v>
+        <v>44.4</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -995,7 +995,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>43.5</v>
+        <v>50</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1015,37 +1015,37 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>39.8</v>
+        <v>35</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>37.2</v>
+        <v>42.3</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>44.2</v>
+        <v>42.3</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1065,25 +1065,25 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>53.4</v>
+        <v>48.8</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>37.9</v>
+        <v>40.7</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-U</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>58.3</v>
+        <v>52.9</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>45.8</v>
+        <v>52.9</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1126,25 +1126,25 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>48.4</v>
+        <v>54.2</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>39.8</v>
+        <v>35.9</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1153,21 +1153,21 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>45.7</v>
+        <v>56.8</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>45.7</v>
+        <v>35.1</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>42.1</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1198,14 +1198,14 @@
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>45.8</v>
+        <v>37.8</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1214,10 +1214,10 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>54.8</v>
+        <v>54.2</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>38.7</v>
+        <v>50</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>66.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>35</v>
+        <v>44.2</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1275,21 +1275,21 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>69</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>41.4</v>
+        <v>44.4</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>52.6</v>
+        <v>44.3</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1320,14 +1320,14 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>38.9</v>
+        <v>45.2</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1336,21 +1336,21 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>43.8</v>
+        <v>56</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>40.6</v>
+        <v>64</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>57.1</v>
+        <v>60</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1381,14 +1381,14 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>42.9</v>
+        <v>43.8</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>64.3</v>
+        <v>61.9</v>
       </c>
       <c r="L15" s="4" t="n">
         <v>42</v>
@@ -1408,7 +1408,7 @@
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>40.5</v>
+        <v>45.2</v>
       </c>
       <c r="O15" s="4" t="n">
         <v>42</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>44.8</v>
+        <v>47.5</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1442,14 +1442,14 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>37.3</v>
+        <v>46.7</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>47.2</v>
+        <v>44.7</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>37.7</v>
+        <v>46.8</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1492,25 +1492,25 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>61</v>
+        <v>42.2</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>45.8</v>
+        <v>48.2</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-D</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1519,21 +1519,21 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>46.7</v>
+        <v>46.2</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>40</v>
+        <v>53.8</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1553,48 +1553,48 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>43.9</v>
+        <v>37.1</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>47</v>
+        <v>40.3</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>36.7</v>
+        <v>39</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>51</v>
+        <v>46.3</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1614,25 +1614,25 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>56.1</v>
+        <v>42.6</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>34.5</v>
+        <v>40.9</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>57.4</v>
+        <v>45.8</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>35.2</v>
+        <v>43.8</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
@@ -1666,46 +1666,46 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>40</v>
+        <v>35.7</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>115</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>44.3</v>
+        <v>40</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>115</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>36</v>
+        <v>39.4</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>50</v>
+        <v>48.5</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1736,37 +1736,37 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>43.9</v>
+        <v>37.7</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-U</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G21" s="3" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>173</v>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-D</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="K21" s="3" t="n">
-        <v>50.8</v>
+        <v>34.7</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>50.8</v>
+        <v>44.4</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1797,25 +1797,25 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>53</v>
+        <v>60.4</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>41.9</v>
+        <v>38.6</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-U-U-D</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1824,21 +1824,21 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>44.7</v>
+        <v>47.5</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>40.4</v>
+        <v>37.5</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1858,25 +1858,25 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>35.8</v>
+        <v>36.6</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>40.9</v>
+        <v>39.8</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>38.1</v>
+        <v>36.9</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="N23" s="3" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>81.8</v>
+        <v>83.3</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1930,14 +1930,14 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>44.8</v>
+        <v>45.8</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1946,10 +1946,10 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>77.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>45</v>
+        <v>55.6</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1980,37 +1980,37 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>55.4</v>
+        <v>36.4</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>40.5</v>
+        <v>39</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-D</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>62.5</v>
+        <v>41.2</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>50</v>
+        <v>47.1</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2041,25 +2041,25 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>60.8</v>
+        <v>61.6</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>50</v>
+        <v>34.9</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2068,21 +2068,21 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>59.3</v>
+        <v>55</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>48.1</v>
+        <v>35</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>44</v>
+        <v>41.9</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>72.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>40.9</v>
+        <v>40.7</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>63.9</v>
+        <v>63.6</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -2174,14 +2174,14 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>40.2</v>
+        <v>35.6</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2190,21 +2190,21 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>56.8</v>
+        <v>56.4</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>40.5</v>
+        <v>38.5</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -2235,14 +2235,14 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>42.4</v>
+        <v>37.2</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>38.5</v>
+        <v>39</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>47</v>
+        <v>45.9</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2296,14 +2296,14 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>39.1</v>
+        <v>42.9</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2312,21 +2312,21 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>44.4</v>
+        <v>51.4</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>42.6</v>
+        <v>40.5</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31">
@@ -2337,57 +2337,57 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D31" s="3" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>110</v>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="G31" s="3" t="n">
-        <v>43.6</v>
+        <v>39.8</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>57.1</v>
+        <v>34.3</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>33.3</v>
+        <v>45.7</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>38.4</v>
+        <v>45.4</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-U</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>85.2</v>
+        <v>54.2</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>51.9</v>
+        <v>41.7</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>47.7</v>
+        <v>56.5</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2479,14 +2479,14 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>54.5</v>
+        <v>47.8</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2495,21 +2495,21 @@
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>59.1</v>
+        <v>60</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N33" s="3" t="n">
-        <v>59.1</v>
+        <v>40</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2529,25 +2529,25 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>53.9</v>
+        <v>49.6</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>39.3</v>
+        <v>45.3</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2556,21 +2556,21 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>60.7</v>
+        <v>51.4</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>50.6</v>
+        <v>53.3</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2601,14 +2601,14 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>39.3</v>
+        <v>38.9</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2617,21 +2617,21 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>51.4</v>
+        <v>48.6</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>40.5</v>
+        <v>54.3</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36">
@@ -2642,19 +2642,19 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>37.5</v>
+        <v>63</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2662,26 +2662,26 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-D</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>53.3</v>
+        <v>80</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>40.6</v>
+        <v>40.2</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2723,10 +2723,10 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>41.5</v>
+        <v>41.1</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>47.5</v>
+        <v>48.8</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2773,25 +2773,25 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>62.7</v>
+        <v>48.7</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>34.3</v>
+        <v>38.2</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-U</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2800,21 +2800,21 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>58.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>37.5</v>
+        <v>47.8</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2834,10 +2834,10 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>254</v>
+        <v>101</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2845,37 +2845,37 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>N-N-N-D</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="L39" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="H39" s="4" t="n">
-        <v>254</v>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>D-N-N-N</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="L39" s="4" t="n">
-        <v>53</v>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="n">
-        <v>39.6</v>
-      </c>
       <c r="O39" s="4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2895,25 +2895,25 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>171</v>
+        <v>98</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>49.1</v>
+        <v>37.8</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>171</v>
+        <v>98</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>84.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>83</v>
+        <v>42</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>50.6</v>
+        <v>35.7</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>83</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>40.4</v>
+        <v>38.3</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2967,14 +2967,14 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>43.3</v>
+        <v>46.6</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -2983,21 +2983,21 @@
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>45.5</v>
+        <v>39.3</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>40.9</v>
+        <v>49.2</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>22</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42">
@@ -3008,19 +3008,19 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>47</v>
+        <v>38.3</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>83</v>
+        <v>167</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -3028,14 +3028,14 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>41</v>
+        <v>44.3</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>83</v>
+        <v>167</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-D</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>46.9</v>
+        <v>47.1</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>43.8</v>
+        <v>44.1</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="43">
@@ -3069,19 +3069,19 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>43.2</v>
+        <v>38.1</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -3089,14 +3089,14 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>40.9</v>
+        <v>48.8</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-D</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3105,21 +3105,21 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>52.4</v>
+        <v>38.9</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>38.1</v>
+        <v>44.4</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44">
@@ -3130,34 +3130,34 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>40.6</v>
+        <v>37.3</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>44.6</v>
+        <v>42.9</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>39.1</v>
+        <v>40</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>50.6</v>
+        <v>45.7</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>57</v>
+        <v>56.3</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -3211,14 +3211,14 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>40.7</v>
+        <v>40.2</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>57.7</v>
+        <v>55.2</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>34.6</v>
+        <v>44.8</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3261,25 +3261,25 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>42.5</v>
+        <v>36</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>43.5</v>
+        <v>42.6</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>48</v>
+        <v>39.5</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>60</v>
+        <v>43.2</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>25</v>
+        <v>81</v>
       </c>
     </row>
     <row r="47">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3322,48 +3322,48 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>37.2</v>
+        <v>39.9</v>
       </c>
       <c r="E47" s="4" t="n">
         <v>148</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>45.9</v>
+        <v>48</v>
       </c>
       <c r="H47" s="4" t="n">
         <v>148</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>44.3</v>
+        <v>42.6</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>50</v>
+        <v>51.5</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3383,25 +3383,25 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>55.4</v>
+        <v>58.4</v>
       </c>
       <c r="E48" s="4" t="n">
         <v>101</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>37.6</v>
+        <v>35.6</v>
       </c>
       <c r="H48" s="4" t="n">
         <v>101</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3410,21 +3410,21 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>43.3</v>
+        <v>40.6</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>36.7</v>
+        <v>37.5</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>72.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3455,14 +3455,14 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>50</v>
+        <v>45.2</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-U</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>75.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>57.6</v>
+        <v>45.7</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="50">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>67.40000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E50" s="4" t="n">
         <v>92</v>
@@ -3516,14 +3516,14 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="H50" s="4" t="n">
         <v>92</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>73.3</v>
+        <v>58.7</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>46.7</v>
+        <v>43.5</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3566,48 +3566,48 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>51.9</v>
+        <v>53.2</v>
       </c>
       <c r="E51" s="4" t="n">
         <v>77</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>44.2</v>
+        <v>39</v>
       </c>
       <c r="H51" s="4" t="n">
         <v>77</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>37.5</v>
+        <v>55.9</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>45</v>
+        <v>41.2</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3627,25 +3627,25 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>48.8</v>
+        <v>61.4</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>39.5</v>
+        <v>42.2</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-D</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3654,21 +3654,21 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>40.5</v>
+        <v>50</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>45.2</v>
+        <v>60</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3688,25 +3688,25 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>82</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>40</v>
+        <v>34.9</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-U</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3715,21 +3715,21 @@
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>83</v>
+        <v>64.3</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>42.6</v>
+        <v>46.4</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3749,37 +3749,37 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>59.8</v>
+        <v>55.1</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>37.8</v>
+        <v>41</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>66.7</v>
+        <v>41.4</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>46.7</v>
+        <v>51.7</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3810,10 +3810,10 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>37.8</v>
+        <v>40</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3821,37 +3821,37 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>37.8</v>
+        <v>41.4</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>36.7</v>
+        <v>39.3</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -4027,67 +4027,67 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>40.7</v>
+        <v>73.3</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-U</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M2" s="3" t="n">
-        <v>75</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>50</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -4098,67 +4098,67 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>46.4</v>
+        <v>38.1</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>35.7</v>
+        <v>57.1</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -4169,44 +4169,44 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>57.1</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>57.1</v>
+        <v>52.6</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-D</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -4215,21 +4215,21 @@
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -4240,17 +4240,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -4259,10 +4259,10 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -4270,37 +4270,37 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>57.1</v>
+        <v>56.2</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-D</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -4311,17 +4311,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -4330,48 +4330,48 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>53.8</v>
+        <v>45.5</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>69.2</v>
+        <v>45.5</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-N</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
         <v>100</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -4382,67 +4382,67 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>N-N-D-D</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="n">
         <v>66.7</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>N-N-N-D</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="N7" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4453,67 +4453,67 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>U-N-D-D</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="N8" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="P8" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J8" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>U-U-N-D</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="N8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>40</v>
-      </c>
       <c r="Q8" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -4524,17 +4524,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -4543,30 +4543,30 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>57.9</v>
+        <v>44.4</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>42.1</v>
+        <v>33.3</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M9" s="3" t="n">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
@@ -4595,17 +4595,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -4614,25 +4614,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>58.3</v>
+        <v>58.8</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>41.7</v>
+        <v>47.1</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-U</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -4641,21 +4641,21 @@
         </is>
       </c>
       <c r="M10" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -4666,17 +4666,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -4685,48 +4685,48 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>N-U-U-U</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J11" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>D-N-U-U</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>85.7</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="n">
-        <v>57.1</v>
-      </c>
       <c r="Q11" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -4737,17 +4737,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -4756,10 +4756,10 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>55.6</v>
+        <v>81.8</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
@@ -4767,14 +4767,14 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>72.2</v>
+        <v>45.5</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>83.3</v>
+        <v>66.7</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>66.7</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -4808,17 +4808,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -4827,10 +4827,10 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>83.3</v>
+        <v>72</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
@@ -4838,14 +4838,14 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>58.3</v>
+        <v>44</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -4854,21 +4854,21 @@
         </is>
       </c>
       <c r="M13" s="3" t="n">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>33.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -4879,17 +4879,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -4898,7 +4898,7 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>61.9</v>
+        <v>42.9</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>21</v>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -4950,17 +4950,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -4969,48 +4969,48 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>56.2</v>
+        <v>47.8</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>56.2</v>
+        <v>39.1</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M15" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>75</v>
+        <v>44.4</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -5021,17 +5021,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -5040,10 +5040,10 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>41.7</v>
+        <v>55</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -5051,37 +5051,37 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>41.7</v>
+        <v>65</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -5092,17 +5092,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>N-N-D-D</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G17" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>D-N-N-D</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="N17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>100</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -5163,67 +5163,67 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
         <v>50</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M18" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -5234,44 +5234,44 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>72</v>
+        <v>40.9</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>36</v>
+        <v>45.5</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>80</v>
+        <v>55.6</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -5305,56 +5305,56 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>43.8</v>
+        <v>42.1</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>50</v>
+        <v>36.8</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -5376,29 +5376,29 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -5406,23 +5406,23 @@
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>44.4</v>
+        <v>40</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M21" s="3" t="n">
-        <v>53.8</v>
+        <v>38.5</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>13</v>
@@ -5433,7 +5433,7 @@
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>46.2</v>
+        <v>53.8</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>13</v>
@@ -5447,17 +5447,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -5466,48 +5466,48 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-D</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N22" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="n">
         <v>55.6</v>
       </c>
-      <c r="G22" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>27</v>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>D-D-U-U</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="N22" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>35.7</v>
-      </c>
       <c r="Q22" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -5518,67 +5518,67 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-U</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="N23" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="n">
         <v>46.2</v>
       </c>
-      <c r="G23" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>26</v>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-D</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="N23" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>45.5</v>
-      </c>
       <c r="Q23" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -5589,17 +5589,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -5608,25 +5608,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>41.2</v>
+        <v>44.1</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -5638,18 +5638,18 @@
         <v>100</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
@@ -5660,67 +5660,67 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>45.5</v>
+        <v>38.5</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>54.5</v>
+        <v>46.2</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-D</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M25" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
-        <v>75</v>
+        <v>33.3</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -5731,17 +5731,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -5750,25 +5750,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>81.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>45.5</v>
+        <v>41.2</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -5777,21 +5777,21 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -5802,17 +5802,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -5821,48 +5821,48 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>56.2</v>
+        <v>75</v>
       </c>
       <c r="G27" s="4" t="n">
         <v>16</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -5873,17 +5873,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -5892,25 +5892,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>38.1</v>
+        <v>45.2</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
       <c r="Q28" s="4" t="n">
         <v>9</v>
@@ -5944,17 +5944,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -5963,25 +5963,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>68.2</v>
+        <v>62.5</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>40.9</v>
+        <v>43.8</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-U</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -5990,21 +5990,21 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -6015,17 +6015,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -6034,48 +6034,48 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>73.09999999999999</v>
+        <v>45.8</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>38.5</v>
+        <v>41.7</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>77.8</v>
+        <v>50</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -6086,44 +6086,44 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>35.3</v>
+        <v>57.1</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>47.1</v>
+        <v>38.1</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -6132,21 +6132,21 @@
         </is>
       </c>
       <c r="M31" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P31" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -6157,17 +6157,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -6176,48 +6176,48 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>77.8</v>
+        <v>57.7</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>38.9</v>
+        <v>46.2</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-U</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>66.7</v>
+        <v>44.4</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -6228,17 +6228,17 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -6247,48 +6247,48 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>54.5</v>
+        <v>44.4</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>45.5</v>
+        <v>44.4</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M33" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P33" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -6299,17 +6299,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -6318,48 +6318,48 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>61.1</v>
+        <v>56.5</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>N-U-U-D</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J34" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>D-N-U-U</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="N34" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>40</v>
-      </c>
       <c r="Q34" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -6370,17 +6370,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -6389,25 +6389,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>52.4</v>
+        <v>66.7</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>21</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>33.3</v>
+        <v>38.1</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-N-U-D</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="M35" s="3" t="n">
-        <v>44.4</v>
+        <v>57.1</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>44.4</v>
+        <v>42.9</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -6441,17 +6441,17 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -6460,10 +6460,10 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -6471,19 +6471,19 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-D</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M36" s="3" t="n">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -6527,25 +6527,25 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>44.4</v>
+        <v>42.9</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>44.4</v>
+        <v>46.4</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
@@ -6554,25 +6554,25 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M37" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P37" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -6602,25 +6602,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>42.1</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>19</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>36.8</v>
+        <v>47.4</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-U</t>
+          <t>N-N-U-U</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -6629,21 +6629,21 @@
         </is>
       </c>
       <c r="M38" s="3" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -6654,17 +6654,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -6673,10 +6673,10 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>72.5</v>
+        <v>80</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -6684,14 +6684,14 @@
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>43.1</v>
+        <v>45</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -6700,21 +6700,21 @@
         </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>94.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P39" s="3" t="n">
-        <v>41.2</v>
+        <v>50</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
@@ -6725,17 +6725,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -6744,10 +6744,10 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -6755,14 +6755,14 @@
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>52.9</v>
+        <v>37.5</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-D</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -6771,21 +6771,21 @@
         </is>
       </c>
       <c r="M40" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P40" s="3" t="n">
-        <v>63.2</v>
+        <v>40</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
@@ -6796,17 +6796,17 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>44.4</v>
+        <v>41.7</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -6826,14 +6826,14 @@
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>48.1</v>
+        <v>50</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -6842,10 +6842,10 @@
         </is>
       </c>
       <c r="M41" s="3" t="n">
-        <v>60</v>
+        <v>46.2</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -6853,10 +6853,10 @@
         </is>
       </c>
       <c r="P41" s="3" t="n">
-        <v>60</v>
+        <v>46.2</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42">
@@ -6867,29 +6867,29 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>33.3</v>
+        <v>44.8</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -6897,37 +6897,37 @@
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>41.7</v>
+        <v>44.8</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-D</t>
+          <t>N-U-D-U</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M42" s="3" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P42" s="3" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -6938,44 +6938,44 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>56.2</v>
+        <v>41.7</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>37.5</v>
+        <v>41.7</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-D</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -6984,21 +6984,21 @@
         </is>
       </c>
       <c r="M43" s="3" t="n">
-        <v>83.3</v>
+        <v>60</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P43" s="3" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -7009,29 +7009,29 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>53.1</v>
+        <v>39.4</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -7039,37 +7039,37 @@
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>46.9</v>
+        <v>57.6</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M44" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P44" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>45</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
@@ -7110,37 +7110,37 @@
         </is>
       </c>
       <c r="I45" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-U</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J45" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>D-U-U-U</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>80</v>
-      </c>
       <c r="N45" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P45" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
@@ -7151,67 +7151,67 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="I46" s="3" t="n">
-        <v>39.4</v>
+        <v>46.7</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M46" s="3" t="n">
-        <v>50</v>
+        <v>43.8</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P46" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
@@ -7222,56 +7222,56 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="J47" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>U-D-U-D</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G47" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I47" s="3" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="J47" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-U</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M47" s="3" t="n">
-        <v>46.7</v>
-      </c>
       <c r="N47" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48">
@@ -7293,17 +7293,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -7312,48 +7312,48 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>66.7</v>
+        <v>53.3</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>44.4</v>
+        <v>53.3</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -7364,17 +7364,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -7383,25 +7383,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>70.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>62.5</v>
+        <v>40.6</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-U</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -7410,10 +7410,10 @@
         </is>
       </c>
       <c r="M49" s="3" t="n">
-        <v>85.7</v>
+        <v>66.7</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -7421,10 +7421,10 @@
         </is>
       </c>
       <c r="P49" s="3" t="n">
-        <v>85.7</v>
+        <v>60</v>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
@@ -7435,17 +7435,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -7454,10 +7454,10 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>70</v>
+        <v>63.6</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -7465,14 +7465,14 @@
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>45</v>
+        <v>36.4</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-U</t>
+          <t>N-U-U-N</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -7481,10 +7481,10 @@
         </is>
       </c>
       <c r="M50" s="3" t="n">
-        <v>87.5</v>
+        <v>54.5</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="P50" s="3" t="n">
-        <v>50</v>
+        <v>54.5</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51">
@@ -7506,17 +7506,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -7525,25 +7525,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>76.5</v>
+        <v>52.9</v>
       </c>
       <c r="G51" s="4" t="n">
         <v>17</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>47.1</v>
+        <v>41.2</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -7552,21 +7552,21 @@
         </is>
       </c>
       <c r="M51" s="3" t="n">
-        <v>66.7</v>
+        <v>62.5</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P51" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
@@ -7577,56 +7577,56 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>40</v>
+        <v>86.7</v>
       </c>
       <c r="G52" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>40</v>
+        <v>53.3</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-D</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -7634,10 +7634,10 @@
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -7648,17 +7648,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -7667,25 +7667,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>81</v>
+        <v>78.3</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>47.6</v>
+        <v>34.8</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-U</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -7694,18 +7694,18 @@
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>87.5</v>
+        <v>75</v>
       </c>
       <c r="N53" s="4" t="n">
         <v>8</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P53" s="3" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="Q53" s="4" t="n">
         <v>8</v>
@@ -7719,67 +7719,67 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>40</v>
+        <v>55.6</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>53.3</v>
+        <v>44.4</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-N-D-U</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M54" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P54" s="3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -7790,49 +7790,49 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Pazartesi</t>
+          <t>Salı</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M55" s="3" t="n">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P55" s="3" t="n">

--- a/BIS_usa.xlsx
+++ b/BIS_usa.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -577,25 +577,25 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>40.4</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>39.4</v>
+        <v>40</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-D</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -604,21 +604,21 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>37.5</v>
+        <v>63.6</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>39.6</v>
+        <v>45.5</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -638,25 +638,25 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>43</v>
+        <v>44.4</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>42</v>
+        <v>49.2</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>48.9</v>
+        <v>45.7</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>43.5</v>
+        <v>46.9</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
@@ -690,7 +690,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -699,25 +699,25 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>38.6</v>
+        <v>40</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>45.7</v>
+        <v>46.2</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
         <v>45.5</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
@@ -737,10 +737,10 @@
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>51.5</v>
+        <v>45.5</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -751,7 +751,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -760,48 +760,48 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>38.9</v>
+        <v>34.8</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>72</v>
+        <v>138</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>138</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>N-D-D-U</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n">
         <v>48.6</v>
       </c>
-      <c r="H5" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>D-N-D-D</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>50</v>
-      </c>
       <c r="O5" s="4" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -812,7 +812,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -821,25 +821,25 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>59.1</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>51.5</v>
+        <v>45.8</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -848,21 +848,21 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>50</v>
+        <v>72.7</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -873,7 +873,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -882,48 +882,48 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>44.3</v>
+        <v>48.3</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>34.1</v>
+        <v>40.2</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-D</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>45.5</v>
+        <v>40</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>63.6</v>
+        <v>56.7</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -934,7 +934,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -943,48 +943,48 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>43.8</v>
+        <v>51.6</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>39.7</v>
+        <v>39.1</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-D</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>48.1</v>
+        <v>38.9</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>44.4</v>
+        <v>55.6</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -995,7 +995,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1007,22 +1007,22 @@
         <v>50</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>35</v>
+        <v>40.9</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>42.3</v>
+        <v>39.3</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>42.3</v>
+        <v>46.4</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>48.8</v>
+        <v>40.5</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1076,14 +1076,14 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>40.7</v>
+        <v>36.7</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-U</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1092,21 +1092,21 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>52.9</v>
+        <v>54.5</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>52.9</v>
+        <v>36.4</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -1117,57 +1117,57 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>54.2</v>
+        <v>39.5</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>35.9</v>
+        <v>41.2</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-U</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>56.8</v>
+        <v>38.5</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>35.1</v>
+        <v>38.5</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1187,25 +1187,25 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>65.90000000000001</v>
+        <v>62.2</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
         <v>37.8</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1214,21 +1214,21 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>54.2</v>
+        <v>61.3</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>50</v>
+        <v>38.7</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>57.4</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>44.2</v>
+        <v>39.6</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>42.1</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>44.4</v>
+        <v>36.8</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>44.3</v>
+        <v>43.4</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1320,14 +1320,14 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>45.2</v>
+        <v>46.5</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>56</v>
+        <v>38.9</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>64</v>
+        <v>44.4</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>60</v>
+        <v>58.9</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1381,14 +1381,14 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>43.8</v>
+        <v>42.1</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>61.9</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>45.2</v>
+        <v>52.6</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
@@ -1422,34 +1422,34 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>47.5</v>
+        <v>40.4</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>46.7</v>
+        <v>38.6</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>44.7</v>
+        <v>46.5</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>46.8</v>
+        <v>46.5</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1492,25 +1492,25 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>42.2</v>
+        <v>42.7</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>48.2</v>
+        <v>38.5</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-D</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1519,21 +1519,21 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>46.2</v>
+        <v>45</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>53.8</v>
+        <v>35</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1553,37 +1553,37 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>37.1</v>
+        <v>41.7</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G18" s="3" t="n">
-        <v>40.3</v>
+        <v>43.9</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K18" s="3" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="N18" s="3" t="n">
-        <v>46.3</v>
+        <v>46</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>42.6</v>
+        <v>42</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1625,14 +1625,14 @@
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>40.9</v>
+        <v>50.7</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1641,21 +1641,21 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>45.8</v>
+        <v>35.7</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>43.8</v>
+        <v>46.4</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1666,57 +1666,57 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>35.7</v>
+        <v>53</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>40</v>
+        <v>39.4</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>39.4</v>
+        <v>37.5</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -1727,34 +1727,34 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>37.7</v>
+        <v>34.7</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>44.4</v>
+        <v>43.1</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="K21" s="3" t="n">
-        <v>34.7</v>
+        <v>36.8</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N21" s="3" t="n">
-        <v>44.4</v>
+        <v>52.6</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1797,25 +1797,25 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>60.4</v>
+        <v>49</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>38.6</v>
+        <v>40</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1824,21 +1824,21 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>47.5</v>
+        <v>55.6</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>37.5</v>
+        <v>38.9</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>36.6</v>
+        <v>40.2</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1869,37 +1869,37 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>39.8</v>
+        <v>41.5</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>36.9</v>
+        <v>35.5</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N23" s="3" t="n">
-        <v>40</v>
+        <v>45.2</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>83.3</v>
+        <v>82.8</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>120</v>
+        <v>267</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1930,14 +1930,14 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>45.8</v>
+        <v>50.2</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>120</v>
+        <v>267</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-D</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1946,10 +1946,10 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>55.6</v>
+        <v>46.6</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>63</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1980,37 +1980,37 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>36.4</v>
+        <v>40.6</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>41.2</v>
+        <v>42.1</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>47.1</v>
+        <v>42.1</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>61.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -2052,14 +2052,14 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>34.9</v>
+        <v>41.2</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-D</t>
+          <t>N-N-D-U</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2068,21 +2068,21 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>55</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>35</v>
+        <v>39.3</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>67.7</v>
+        <v>76.2</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>41.9</v>
+        <v>42.9</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>40.7</v>
+        <v>40</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2163,25 +2163,25 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>63.6</v>
+        <v>54.8</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>35.6</v>
+        <v>39.3</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2190,21 +2190,21 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>56.4</v>
+        <v>54.1</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>38.5</v>
+        <v>40.5</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>73.3</v>
+        <v>81.2</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -2235,14 +2235,14 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>37.2</v>
+        <v>41.2</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-D</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>80.5</v>
+        <v>87.5</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>45.9</v>
+        <v>48.5</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2296,14 +2296,14 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>42.9</v>
+        <v>41.2</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2312,21 +2312,21 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>51.4</v>
+        <v>54.5</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>40.5</v>
+        <v>43.6</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2346,10 +2346,10 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>38.9</v>
+        <v>47.3</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2357,37 +2357,37 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>39.8</v>
+        <v>37.4</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="L31" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
           <t>D/U</t>
         </is>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>34.3</v>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N31" s="3" t="n">
-        <v>45.7</v>
+        <v>35.5</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2407,10 +2407,10 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>53.6</v>
+        <v>46.9</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2418,14 +2418,14 @@
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>45.4</v>
+        <v>46.9</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>54.2</v>
+        <v>50</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>41.7</v>
+        <v>43.3</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
@@ -2459,19 +2459,19 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>56.5</v>
+        <v>38.1</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2479,37 +2479,37 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>N-D-N-N</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N33" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>49.6</v>
+        <v>36.9</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2540,14 +2540,14 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>45.3</v>
+        <v>44</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>51.4</v>
+        <v>38.5</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>42.9</v>
+        <v>44.2</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>53.3</v>
+        <v>49.4</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2601,14 +2601,14 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>38.9</v>
+        <v>40.2</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-D</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>48.6</v>
+        <v>60.9</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>54.3</v>
+        <v>52.2</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36">
@@ -2642,19 +2642,19 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>63</v>
+        <v>47.5</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>27</v>
+        <v>179</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2662,26 +2662,26 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>48.1</v>
+        <v>48.6</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>27</v>
+        <v>179</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>60</v>
+        <v>56.8</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>80</v>
+        <v>54.1</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2712,37 +2712,37 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>40.2</v>
+        <v>45</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>41.1</v>
+        <v>45</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>39</v>
+        <v>38.6</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
@@ -2750,10 +2750,10 @@
         </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>48.8</v>
+        <v>43.2</v>
       </c>
       <c r="O37" s="4" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="38">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2773,25 +2773,25 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>48.7</v>
+        <v>35.1</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>38.2</v>
+        <v>41.8</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-U</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2800,21 +2800,21 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>47.8</v>
+        <v>48.3</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2834,10 +2834,10 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>78.2</v>
+        <v>80.7</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2845,14 +2845,14 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>49.5</v>
+        <v>48.2</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-D</t>
+          <t>N-N-D-N</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="N39" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="O39" s="4" t="n">
         <v>50</v>
-      </c>
-      <c r="O39" s="4" t="n">
-        <v>54</v>
       </c>
     </row>
     <row r="40">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2895,25 +2895,25 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>37.8</v>
+        <v>46.9</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-D</t>
+          <t>N-N-D-N</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>78.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>35.7</v>
+        <v>62.1</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41">
@@ -2947,57 +2947,57 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>38.3</v>
+        <v>38.1</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>46.6</v>
+        <v>38.1</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>133</v>
+        <v>21</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>U-U-N-N</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>39.3</v>
+        <v>36.4</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>49.2</v>
+        <v>45.5</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>61</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42">
@@ -3008,19 +3008,19 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>38.3</v>
+        <v>41.5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -3028,14 +3028,14 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>44.3</v>
+        <v>38.4</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>47.1</v>
+        <v>37.8</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>44.1</v>
+        <v>40.5</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43">
@@ -3069,19 +3069,19 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>38.1</v>
+        <v>35.5</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -3089,26 +3089,26 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>48.8</v>
+        <v>40.8</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>38.9</v>
+        <v>50</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>44.4</v>
+        <v>42.3</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44">
@@ -3130,19 +3130,19 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
         <v>37.3</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -3150,14 +3150,14 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>42.9</v>
+        <v>47.6</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3166,21 +3166,21 @@
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>40</v>
+        <v>38.4</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>45.7</v>
+        <v>45.2</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3200,25 +3200,25 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>56.3</v>
+        <v>56.7</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>40.2</v>
+        <v>48.5</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>55.2</v>
+        <v>45.7</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>44.8</v>
+        <v>54.3</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3261,25 +3261,25 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>36</v>
+        <v>38.2</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>42.6</v>
+        <v>44.1</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3288,21 +3288,21 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>39.5</v>
+        <v>34.2</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>43.2</v>
+        <v>43.8</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3322,48 +3322,48 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>39.9</v>
+        <v>37.6</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>48</v>
+        <v>46.3</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>42.6</v>
+        <v>43.7</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>51.5</v>
+        <v>50.7</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>58.4</v>
+        <v>60.4</v>
       </c>
       <c r="E48" s="4" t="n">
         <v>101</v>
@@ -3394,14 +3394,14 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>35.6</v>
+        <v>38.6</v>
       </c>
       <c r="H48" s="4" t="n">
         <v>101</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>40.6</v>
+        <v>61.3</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>37.5</v>
+        <v>41.9</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>64.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3455,14 +3455,14 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>45.2</v>
+        <v>38.6</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3471,21 +3471,21 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>45.7</v>
+        <v>38.1</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3505,25 +3505,25 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>37</v>
+        <v>40.8</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>58.7</v>
+        <v>82.8</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>43.5</v>
+        <v>37.9</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3566,25 +3566,25 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>53.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>39</v>
+        <v>45.1</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3593,21 +3593,21 @@
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>55.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>41.2</v>
+        <v>42.9</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52">
@@ -3618,57 +3618,57 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>61.4</v>
+        <v>38.5</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>42.2</v>
+        <v>42.6</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>50</v>
+        <v>40.4</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>60</v>
+        <v>38.3</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3688,25 +3688,25 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>72.09999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>34.9</v>
+        <v>46.7</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3715,21 +3715,21 @@
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>64.3</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>46.4</v>
+        <v>57.7</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3749,37 +3749,37 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>55.1</v>
+        <v>41.6</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>41</v>
+        <v>40.6</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>41.4</v>
+        <v>50</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>51.7</v>
+        <v>50</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3810,34 +3810,34 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>41.4</v>
+        <v>42.7</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>39.3</v>
+        <v>46.4</v>
       </c>
       <c r="L55" s="4" t="n">
         <v>28</v>
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>50</v>
+        <v>46.4</v>
       </c>
       <c r="O55" s="4" t="n">
         <v>28</v>
@@ -4027,67 +4027,67 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>73.3</v>
+        <v>50</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>73.3</v>
+        <v>41.7</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-D</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M2" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -4098,44 +4098,44 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>38.1</v>
+        <v>35.5</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>57.1</v>
+        <v>58.1</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -4144,21 +4144,21 @@
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
         <v>60</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -4169,67 +4169,67 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>36.4</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>52.6</v>
+        <v>54.5</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M4" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -4240,56 +4240,56 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>56.2</v>
+        <v>60</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-D</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -4297,10 +4297,10 @@
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>60</v>
+        <v>77.8</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -4311,17 +4311,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -4330,48 +4330,48 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>45.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>45.5</v>
+        <v>53.8</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-N</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -4382,29 +4382,29 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>46.2</v>
+        <v>52.9</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -4412,37 +4412,37 @@
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>38.5</v>
+        <v>58.8</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-D</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M7" s="3" t="n">
         <v>66.7</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -4453,67 +4453,67 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>41.2</v>
+        <v>61.5</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>35.3</v>
+        <v>38.5</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-D</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M8" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -4524,17 +4524,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -4543,48 +4543,48 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>44.4</v>
+        <v>60</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>55.6</v>
+        <v>60</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>55.6</v>
+        <v>40</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -4595,44 +4595,44 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-D</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>58.8</v>
+        <v>35.7</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>47.1</v>
+        <v>42.9</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-U</t>
+          <t>N-N-U-D</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -4644,18 +4644,18 @@
         <v>50</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -4666,29 +4666,29 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>65.2</v>
+        <v>53.8</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -4696,37 +4696,37 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>43.5</v>
+        <v>53.8</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-U</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -4737,17 +4737,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -4756,25 +4756,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>81.8</v>
+        <v>83.3</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -4808,17 +4808,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -4827,48 +4827,48 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>72</v>
+        <v>53.8</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>44</v>
+        <v>46.2</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M13" s="3" t="n">
-        <v>85.7</v>
+        <v>44.4</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>55.6</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -4879,17 +4879,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -4909,26 +4909,26 @@
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>47.6</v>
+        <v>50</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -4950,17 +4950,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -4969,41 +4969,41 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>47.8</v>
+        <v>70.8</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>39.1</v>
+        <v>33.3</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M15" s="3" t="n">
-        <v>55.6</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N15" s="4" t="n">
         <v>9</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
@@ -5021,17 +5021,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -5040,25 +5040,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>55</v>
+        <v>47.4</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>65</v>
+        <v>47.4</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
@@ -5092,17 +5092,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>40</v>
+        <v>38.9</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -5122,37 +5122,37 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>53.3</v>
+        <v>44.4</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-D</t>
+          <t>N-D-D-U</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -5163,17 +5163,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -5182,10 +5182,10 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>42.9</v>
+        <v>44.8</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -5193,14 +5193,14 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>50</v>
+        <v>41.4</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="M18" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>66.7</v>
+        <v>38.5</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -5234,29 +5234,29 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>40.9</v>
+        <v>60</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -5264,14 +5264,14 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>45.5</v>
+        <v>53.3</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -5280,10 +5280,10 @@
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -5305,53 +5305,53 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>42.1</v>
+        <v>44.4</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>36.8</v>
+        <v>55.6</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>5</v>
@@ -5376,56 +5376,56 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>40</v>
+        <v>41.7</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I21" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-U-D</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M21" s="3" t="n">
-        <v>38.5</v>
+        <v>54.5</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -5433,10 +5433,10 @@
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>53.8</v>
+        <v>63.6</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -5447,17 +5447,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -5466,25 +5466,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>59.1</v>
+        <v>47.1</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>50</v>
+        <v>35.3</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>U-U-D-U</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -5496,18 +5496,18 @@
         <v>66.7</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -5518,17 +5518,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -5537,48 +5537,48 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>42.9</v>
+        <v>57.1</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M23" s="3" t="n">
-        <v>38.5</v>
+        <v>50</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -5589,17 +5589,17 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -5608,25 +5608,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>85.3</v>
+        <v>89.8</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>44.1</v>
+        <v>46.9</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-D</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>44.4</v>
+        <v>48</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
@@ -5660,17 +5660,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -5679,25 +5679,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>38.5</v>
+        <v>55</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -5706,21 +5706,21 @@
         </is>
       </c>
       <c r="M25" s="3" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
-        <v>33.3</v>
+        <v>57.1</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
@@ -5731,17 +5731,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -5750,10 +5750,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>82.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -5761,14 +5761,14 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>41.2</v>
+        <v>43.8</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-D</t>
+          <t>N-N-D-U</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -5777,21 +5777,21 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -5802,17 +5802,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -5821,25 +5821,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>75</v>
+        <v>65.2</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>50</v>
+        <v>43.5</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -5848,7 +5848,7 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>8</v>
@@ -5859,7 +5859,7 @@
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="Q27" s="4" t="n">
         <v>8</v>
@@ -5873,17 +5873,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -5892,10 +5892,10 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>71</v>
+        <v>64.7</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -5903,14 +5903,14 @@
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>45.2</v>
+        <v>58.8</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>55.6</v>
+        <v>44.4</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>9</v>
@@ -5930,7 +5930,7 @@
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>66.7</v>
+        <v>55.6</v>
       </c>
       <c r="Q28" s="4" t="n">
         <v>9</v>
@@ -5944,17 +5944,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -5963,25 +5963,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>62.5</v>
+        <v>84.2</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>43.8</v>
+        <v>42.1</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-D</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -5990,21 +5990,21 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -6015,49 +6015,49 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>45.8</v>
+        <v>37.5</v>
       </c>
       <c r="G30" s="4" t="n">
         <v>24</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>41.7</v>
+        <v>45.8</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M30" s="3" t="n">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P30" s="3" t="n">
@@ -6086,67 +6086,67 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>57.1</v>
+        <v>52.9</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>U-D-N-U</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
         </is>
       </c>
-      <c r="I31" s="3" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-D</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="N31" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="P31" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -6157,17 +6157,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>57.7</v>
+        <v>46.7</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -6187,37 +6187,37 @@
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>46.2</v>
+        <v>46.7</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>55.6</v>
+        <v>60</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>44.4</v>
+        <v>60</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -6228,67 +6228,67 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>44.4</v>
+        <v>100</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>N-D-N-N</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M33" s="3" t="n">
         <v>100</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P33" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -6299,17 +6299,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -6318,48 +6318,48 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>56.5</v>
+        <v>41.9</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>43.5</v>
+        <v>48.4</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>83.3</v>
+        <v>50</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P34" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
@@ -6370,17 +6370,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -6389,25 +6389,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>66.7</v>
+        <v>63.2</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>38.1</v>
+        <v>42.1</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>D-N-U-D</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -6416,21 +6416,21 @@
         </is>
       </c>
       <c r="M35" s="3" t="n">
-        <v>57.1</v>
+        <v>62.5</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -6441,29 +6441,29 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>50</v>
+        <v>55.9</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -6471,26 +6471,26 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>75</v>
+        <v>64.7</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>N-D-U-U</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -6498,10 +6498,10 @@
         </is>
       </c>
       <c r="P36" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -6512,17 +6512,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -6531,37 +6531,37 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>42.9</v>
+        <v>51.5</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>46.4</v>
+        <v>42.4</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M37" s="3" t="n">
-        <v>60</v>
+        <v>38.5</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -6569,10 +6569,10 @@
         </is>
       </c>
       <c r="P37" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
@@ -6583,29 +6583,29 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>42.1</v>
+        <v>50</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -6613,34 +6613,34 @@
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>47.4</v>
+        <v>40.9</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-U</t>
+          <t>N-U-U-D</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M38" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>8</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="Q38" s="4" t="n">
         <v>8</v>
@@ -6654,17 +6654,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -6673,7 +6673,7 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>20</v>
@@ -6684,14 +6684,14 @@
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-D</t>
+          <t>N-N-D-N</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -6700,10 +6700,10 @@
         </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -6711,10 +6711,10 @@
         </is>
       </c>
       <c r="P39" s="3" t="n">
-        <v>50</v>
+        <v>77.8</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
@@ -6725,17 +6725,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -6744,10 +6744,10 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>83.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -6755,14 +6755,14 @@
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>37.5</v>
+        <v>47.6</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-D</t>
+          <t>N-N-D-N</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -6771,21 +6771,21 @@
         </is>
       </c>
       <c r="M40" s="3" t="n">
-        <v>90</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P40" s="3" t="n">
-        <v>40</v>
+        <v>77.8</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
@@ -6796,44 +6796,44 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>41.7</v>
+        <v>60</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-U</t>
+          <t>U-U-N-N</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -6842,21 +6842,21 @@
         </is>
       </c>
       <c r="M41" s="3" t="n">
-        <v>46.2</v>
+        <v>66.7</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P41" s="3" t="n">
-        <v>46.2</v>
+        <v>33.3</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -6867,67 +6867,67 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>44.8</v>
+        <v>37</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>44.8</v>
+        <v>40.7</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-U</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M42" s="3" t="n">
-        <v>60</v>
+        <v>41.7</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P42" s="3" t="n">
-        <v>40</v>
+        <v>41.7</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
@@ -6938,29 +6938,29 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>41.7</v>
+        <v>48</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -6968,37 +6968,37 @@
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>41.7</v>
+        <v>44</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M43" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P43" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -7009,17 +7009,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -7028,10 +7028,10 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>39.4</v>
+        <v>43.8</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -7039,26 +7039,26 @@
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>57.6</v>
+        <v>46.9</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M44" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -7066,10 +7066,10 @@
         </is>
       </c>
       <c r="P44" s="3" t="n">
-        <v>60</v>
+        <v>41.7</v>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45">
@@ -7080,17 +7080,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-D</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7099,48 +7099,48 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>45</v>
+        <v>52.4</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>60</v>
+        <v>47.6</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-D</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M45" s="3" t="n">
-        <v>50</v>
+        <v>41.7</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P45" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46">
@@ -7151,29 +7151,29 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>53.3</v>
+        <v>39.4</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -7181,37 +7181,37 @@
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>46.7</v>
+        <v>45.5</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M46" s="3" t="n">
-        <v>43.8</v>
+        <v>63.6</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>50</v>
+        <v>54.5</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47">
@@ -7222,44 +7222,44 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>34.8</v>
+        <v>51.6</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>52.2</v>
+        <v>61.3</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -7268,21 +7268,21 @@
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48">
@@ -7293,67 +7293,67 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>53.3</v>
+        <v>43.8</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>53.3</v>
+        <v>43.8</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M48" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -7364,17 +7364,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -7383,25 +7383,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>40.6</v>
+        <v>37.5</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -7413,18 +7413,18 @@
         <v>66.7</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P49" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q49" s="4" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
@@ -7435,17 +7435,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-N-D</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -7454,25 +7454,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>63.6</v>
+        <v>62.5</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>36.4</v>
+        <v>50</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>U-U-N-D</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -7481,10 +7481,10 @@
         </is>
       </c>
       <c r="M50" s="3" t="n">
-        <v>54.5</v>
+        <v>85.7</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="P50" s="3" t="n">
-        <v>54.5</v>
+        <v>42.9</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -7506,17 +7506,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -7525,10 +7525,10 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>52.9</v>
+        <v>87.5</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -7536,14 +7536,14 @@
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>41.2</v>
+        <v>37.5</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>D-N-N-N</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -7552,10 +7552,10 @@
         </is>
       </c>
       <c r="M51" s="3" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -7563,10 +7563,10 @@
         </is>
       </c>
       <c r="P51" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -7577,17 +7577,17 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -7596,25 +7596,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>86.7</v>
+        <v>40</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>53.3</v>
+        <v>36</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -7623,21 +7623,21 @@
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>100</v>
+        <v>54.5</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>100</v>
+        <v>45.5</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
@@ -7648,17 +7648,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -7667,25 +7667,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>78.3</v>
+        <v>80</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>34.8</v>
+        <v>65</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -7694,18 +7694,18 @@
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="N53" s="4" t="n">
         <v>8</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P53" s="3" t="n">
-        <v>37.5</v>
+        <v>62.5</v>
       </c>
       <c r="Q53" s="4" t="n">
         <v>8</v>
@@ -7719,29 +7719,29 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>55.6</v>
+        <v>40</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
@@ -7749,37 +7749,37 @@
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>44.4</v>
+        <v>40</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>N-D-U-D</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M54" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P54" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -7790,17 +7790,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Salı</t>
+          <t>Çarşamba</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -7809,25 +7809,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>55.6</v>
+        <v>69.2</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>44.4</v>
+        <v>38.5</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -7839,18 +7839,18 @@
         <v>100</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P55" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/BIS_usa.xlsx
+++ b/BIS_usa.xlsx
@@ -690,7 +690,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -699,48 +699,48 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>40</v>
+        <v>38.2</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>65</v>
+        <v>136</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>46.2</v>
+        <v>39.7</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>65</v>
+        <v>136</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>45.5</v>
+        <v>39.7</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>45.5</v>
+        <v>43.1</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5">
@@ -751,7 +751,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -760,48 +760,48 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>34.8</v>
+        <v>38.7</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>138</v>
+        <v>62</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G5" s="3" t="n">
-        <v>46.4</v>
+        <v>50</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>138</v>
+        <v>62</v>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K5" s="3" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>48.6</v>
+        <v>50</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -812,7 +812,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -821,25 +821,25 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>68.09999999999999</v>
+        <v>53.6</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>45.8</v>
+        <v>41.1</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-U</t>
+          <t>U-N-N-D</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>72.7</v>
+        <v>63.2</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>45.5</v>
+        <v>42.1</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -995,7 +995,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1004,25 +1004,25 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>50</v>
+        <v>53.2</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>40.9</v>
+        <v>40.3</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1031,21 +1031,21 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>39.3</v>
+        <v>64</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>46.4</v>
+        <v>48</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1187,25 +1187,25 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>62.2</v>
+        <v>55.2</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>37.8</v>
+        <v>43.3</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1214,21 +1214,21 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>61.3</v>
+        <v>63.6</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>38.7</v>
+        <v>50</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -1605,34 +1605,34 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>42</v>
+        <v>38.4</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>50.7</v>
+        <v>39.3</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>35.7</v>
+        <v>47.5</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>46.4</v>
+        <v>57.5</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>53</v>
+        <v>40.7</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1686,14 +1686,14 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>39.4</v>
+        <v>43.4</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1702,21 +1702,21 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>37.5</v>
+        <v>41.3</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>50</v>
+        <v>47.8</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>49</v>
+        <v>56.9</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1808,14 +1808,14 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>55.6</v>
+        <v>56.4</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>38.9</v>
+        <v>46.2</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2041,25 +2041,25 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>41.2</v>
+        <v>43</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-U</t>
+          <t>N-N-D-N</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2068,21 +2068,21 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>39.3</v>
+        <v>43.3</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>76.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>42.9</v>
+        <v>37.3</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>70</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>40</v>
+        <v>38.5</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2224,25 +2224,25 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>81.2</v>
+        <v>60.9</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>41.2</v>
+        <v>46.4</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2251,21 +2251,21 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>87.5</v>
+        <v>63</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2285,10 +2285,10 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>48.5</v>
+        <v>45.9</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2296,26 +2296,26 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>41.2</v>
+        <v>42.9</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>54.5</v>
+        <v>40</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>43.6</v>
+        <v>46.7</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2346,10 +2346,10 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>47.3</v>
+        <v>45.8</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2357,14 +2357,14 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>37.4</v>
+        <v>42.4</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2373,21 +2373,21 @@
         </is>
       </c>
       <c r="K31" s="3" t="n">
-        <v>41.9</v>
+        <v>50</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>35.5</v>
+        <v>50</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>49.4</v>
+        <v>47.8</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2601,14 +2601,14 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>40.2</v>
+        <v>42.6</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>60.9</v>
+        <v>60</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>52.2</v>
+        <v>42.9</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2834,25 +2834,25 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>80.7</v>
+        <v>73.8</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>48.2</v>
+        <v>42.6</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>84</v>
+        <v>77.3</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>46</v>
+        <v>36.4</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40">
@@ -2947,46 +2947,46 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>38.1</v>
+        <v>51.4</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-U</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>36.4</v>
+        <v>33.3</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>45.5</v>
+        <v>61.1</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
@@ -3008,19 +3008,19 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>41.5</v>
+        <v>43</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -3028,14 +3028,14 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>38.4</v>
+        <v>47</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>37.8</v>
+        <v>41.7</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>40.5</v>
+        <v>58.3</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>38.2</v>
+        <v>50</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>186</v>
+        <v>50</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -3272,14 +3272,14 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>44.1</v>
+        <v>48</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>186</v>
+        <v>50</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3288,21 +3288,21 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>34.2</v>
+        <v>52.4</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>43.8</v>
+        <v>52.4</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>73</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3322,48 +3322,48 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>37.6</v>
+        <v>43.9</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-D</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G47" s="3" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="H47" s="4" t="n">
-        <v>149</v>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-U</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v>71</v>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N47" s="3" t="n">
-        <v>50.7</v>
+        <v>42.3</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>71</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>60.4</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -3394,14 +3394,14 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>38.6</v>
+        <v>35.2</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3410,21 +3410,21 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>61.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>41.9</v>
+        <v>38.2</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="49">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3688,10 +3688,10 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>73.3</v>
+        <v>60.3</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3699,14 +3699,14 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>46.7</v>
+        <v>41.2</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3715,21 +3715,21 @@
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>53.3</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>57.7</v>
+        <v>43.3</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3810,10 +3810,10 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>48</v>
+        <v>41.5</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3821,14 +3821,14 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>42.7</v>
+        <v>56.6</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3837,21 +3837,21 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>46.4</v>
+        <v>38.5</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -4179,19 +4179,19 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>36.4</v>
+        <v>53.3</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>54.5</v>
+        <v>60</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="M4" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
       <c r="P4" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -4250,57 +4250,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>46.7</v>
+        <v>53.8</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>60</v>
+        <v>69.2</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>N-D-D-N</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>77.8</v>
+        <v>50</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>60</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -4341,14 +4341,14 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>53.8</v>
+        <v>40</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-U</t>
+          <t>U-N-N-D</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -4357,21 +4357,21 @@
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -4534,57 +4534,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>U-D-N-N</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J9" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>U-D-N-U</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>60</v>
-      </c>
       <c r="N9" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>40</v>
+        <v>83.3</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -4747,34 +4747,34 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>83.3</v>
+        <v>45.5</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-D</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>80</v>
+        <v>66.7</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -5244,19 +5244,19 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>60</v>
+        <v>45.8</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -5264,37 +5264,37 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>53.3</v>
+        <v>54.2</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>75</v>
+        <v>42.9</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -5315,46 +5315,46 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>55.6</v>
+        <v>41.7</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>60</v>
+        <v>42.9</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -5466,25 +5466,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>47.1</v>
+        <v>59.3</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>35.3</v>
+        <v>48.1</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="M22" s="3" t="n">
-        <v>66.7</v>
+        <v>63.6</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>50</v>
+        <v>54.5</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -5750,25 +5750,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>68.8</v>
+        <v>70</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>43.8</v>
+        <v>45</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-U</t>
+          <t>N-N-D-N</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -5777,21 +5777,21 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -5821,10 +5821,10 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>65.2</v>
+        <v>75</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -5832,14 +5832,14 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>43.5</v>
+        <v>62.5</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -5848,21 +5848,21 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P27" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -5963,25 +5963,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>84.2</v>
+        <v>53.3</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>42.1</v>
+        <v>40</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -5990,21 +5990,21 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>100</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -6025,57 +6025,57 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>U-U-U</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>37.5</v>
+        <v>42.9</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>45.8</v>
+        <v>61.9</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-U</t>
+          <t>U-U-U-N</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
@@ -6096,57 +6096,57 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>52.9</v>
+        <v>54.5</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>U-D-N-D</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N31" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I31" s="3" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>U-D-N-U</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="N31" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
       <c r="P31" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -6389,48 +6389,48 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>63.2</v>
+        <v>43.5</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>42.1</v>
+        <v>47.8</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-N</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M35" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P35" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -6673,25 +6673,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>90</v>
+        <v>66.7</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>65</v>
+        <v>55.6</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -6700,21 +6700,21 @@
         </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P39" s="3" t="n">
-        <v>77.8</v>
+        <v>66.7</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -6806,39 +6806,39 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>60</v>
+        <v>42.9</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-N</t>
+          <t>U-U-N-U</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M41" s="3" t="n">
@@ -6849,11 +6849,11 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P41" s="3" t="n">
-        <v>33.3</v>
+        <v>66.7</v>
       </c>
       <c r="Q41" s="4" t="n">
         <v>3</v>
@@ -6877,46 +6877,46 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>37</v>
+        <v>40.7</v>
       </c>
       <c r="G42" s="4" t="n">
         <v>27</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>40.7</v>
+        <v>51.9</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M42" s="3" t="n">
-        <v>41.7</v>
+        <v>45.5</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="P42" s="3" t="n">
-        <v>41.7</v>
+        <v>81.8</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -7170,48 +7170,48 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>39.4</v>
+        <v>75</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-N</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="N46" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I46" s="3" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>33</v>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-U</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="N46" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="P46" s="3" t="n">
-        <v>54.5</v>
+        <v>50</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -7241,25 +7241,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>51.6</v>
+        <v>48.1</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>61.3</v>
+        <v>51.9</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
@@ -7268,21 +7268,21 @@
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>58.3</v>
+        <v>50</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
@@ -7303,19 +7303,19 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>43.8</v>
+        <v>70</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -7323,37 +7323,37 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>43.8</v>
+        <v>40</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>80</v>
+        <v>53.8</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
@@ -7678,34 +7678,34 @@
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>65</v>
+        <v>46.2</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-N</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>87.5</v>
+        <v>37.5</v>
       </c>
       <c r="N53" s="4" t="n">
         <v>8</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P53" s="3" t="n">
-        <v>62.5</v>
+        <v>50</v>
       </c>
       <c r="Q53" s="4" t="n">
         <v>8</v>
@@ -7800,43 +7800,43 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>69.2</v>
+        <v>41.7</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J55" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-N</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I55" s="3" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="J55" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-U</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="M55" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N55" s="4" t="n">
         <v>4</v>

--- a/BIS_usa.xlsx
+++ b/BIS_usa.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -577,25 +577,25 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>64.59999999999999</v>
+        <v>51.8</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>40</v>
+        <v>39.8</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>N-D-N-U</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -604,18 +604,18 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>63.6</v>
+        <v>54.5</v>
       </c>
       <c r="L2" s="4" t="n">
         <v>22</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>45.5</v>
+        <v>40.9</v>
       </c>
       <c r="O2" s="4" t="n">
         <v>22</v>
@@ -629,7 +629,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -638,25 +638,25 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>44.4</v>
+        <v>43.4</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>49.2</v>
+        <v>41.4</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>45.7</v>
+        <v>38.7</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>46.9</v>
+        <v>43</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4">
@@ -690,57 +690,57 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>38.2</v>
+        <v>40.3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G4" s="3" t="n">
-        <v>39.7</v>
+        <v>37.3</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K4" s="3" t="n">
-        <v>39.7</v>
+        <v>35.2</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>43.1</v>
+        <v>37</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
@@ -751,7 +751,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -760,48 +760,48 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>D-D-N-U</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n">
         <v>38.7</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>62</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>N-D-D-N</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>42.9</v>
-      </c>
       <c r="L5" s="4" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>50</v>
+        <v>35.5</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -812,7 +812,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -821,25 +821,25 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>53.6</v>
+        <v>51.9</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>41.1</v>
+        <v>42</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-D</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -848,21 +848,21 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>63.2</v>
+        <v>56.5</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>42.1</v>
+        <v>47.8</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -873,7 +873,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -882,10 +882,10 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>48.3</v>
+        <v>55.3</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -893,37 +893,37 @@
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-D</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>40</v>
+        <v>48.6</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>56.7</v>
+        <v>51.4</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -934,7 +934,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>51.6</v>
+        <v>49.4</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -954,26 +954,26 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>39.1</v>
+        <v>37.3</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-D</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>38.9</v>
+        <v>52</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>55.6</v>
+        <v>48</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -995,7 +995,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1004,10 +1004,10 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>53.2</v>
+        <v>43.5</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -1015,14 +1015,14 @@
         </is>
       </c>
       <c r="G9" s="3" t="n">
-        <v>40.3</v>
+        <v>46.4</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="K9" s="3" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>25</v>
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="O9" s="4" t="n">
         <v>25</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>40.5</v>
+        <v>40.3</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -1076,14 +1076,14 @@
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>36.7</v>
+        <v>43.4</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>N-N-U-D</t>
+          <t>N-U-D-D</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>54.5</v>
+        <v>46.2</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>36.4</v>
+        <v>34.6</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11">
@@ -1117,34 +1117,34 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>39.5</v>
+        <v>35.7</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>41.2</v>
+        <v>40</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1153,21 +1153,21 @@
         </is>
       </c>
       <c r="K11" s="3" t="n">
-        <v>38.5</v>
+        <v>38.3</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N11" s="3" t="n">
-        <v>38.5</v>
+        <v>38.3</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1187,25 +1187,25 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>55.2</v>
+        <v>58.4</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G12" s="3" t="n">
-        <v>43.3</v>
+        <v>36</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1214,21 +1214,21 @@
         </is>
       </c>
       <c r="K12" s="3" t="n">
-        <v>63.6</v>
+        <v>48.3</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N12" s="3" t="n">
-        <v>50</v>
+        <v>41.4</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1248,25 +1248,25 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>57.4</v>
+        <v>61.5</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1275,21 +1275,21 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>42.1</v>
+        <v>58.3</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>36.8</v>
+        <v>37.5</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>43.4</v>
+        <v>42.6</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1320,14 +1320,14 @@
         </is>
       </c>
       <c r="G14" s="3" t="n">
-        <v>46.5</v>
+        <v>45.5</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="K14" s="3" t="n">
-        <v>38.9</v>
+        <v>38.7</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>44.4</v>
+        <v>54.8</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>58.9</v>
+        <v>54.3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1381,14 +1381,14 @@
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>42.1</v>
+        <v>36.2</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>62.2</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>52.6</v>
+        <v>44.4</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16">
@@ -1422,39 +1422,39 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>40.4</v>
+        <v>43</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-U</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>D</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>114</v>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-D</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
         </is>
       </c>
       <c r="K16" s="3" t="n">
@@ -1465,11 +1465,11 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>46.5</v>
+        <v>39.5</v>
       </c>
       <c r="O16" s="4" t="n">
         <v>43</v>
@@ -1483,7 +1483,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1492,25 +1492,25 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>42.7</v>
+        <v>49.7</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>38.5</v>
+        <v>42.1</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1519,21 +1519,21 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>45</v>
+        <v>47.2</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>35</v>
+        <v>47.2</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="18">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1553,48 +1553,48 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>139</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
         <v>41.7</v>
       </c>
-      <c r="E18" s="4" t="n">
-        <v>132</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="H18" s="4" t="n">
+        <v>139</v>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-U</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G18" s="3" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>132</v>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-D</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N18" s="3" t="n">
-        <v>46</v>
+        <v>40.4</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
@@ -1605,46 +1605,46 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>38.4</v>
+        <v>37.9</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G19" s="3" t="n">
-        <v>39.3</v>
+        <v>40.5</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K19" s="3" t="n">
-        <v>47.5</v>
+        <v>38.6</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="N19" s="3" t="n">
-        <v>57.5</v>
+        <v>50</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1675,48 +1675,48 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>40.7</v>
+        <v>40</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>43.4</v>
+        <v>40.8</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>41.3</v>
+        <v>36.7</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>47.8</v>
+        <v>42.9</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -1727,19 +1727,19 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>34.7</v>
+        <v>34.9</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1747,37 +1747,37 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>43.1</v>
+        <v>44.3</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="K21" s="3" t="n">
-        <v>36.8</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>57</v>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="N21" s="3" t="n">
-        <v>52.6</v>
+        <v>48.4</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>56.9</v>
+        <v>53.6</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1808,14 +1808,14 @@
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>44</v>
+        <v>43.6</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>56.4</v>
+        <v>47.9</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>46.2</v>
+        <v>45.8</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1858,48 +1858,48 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>40.2</v>
+        <v>59.3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>41.5</v>
+        <v>38.3</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>35.5</v>
+        <v>53.1</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N23" s="3" t="n">
-        <v>45.2</v>
+        <v>43.8</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
@@ -1930,7 +1930,7 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>50.2</v>
+        <v>50.6</v>
       </c>
       <c r="H24" s="4" t="n">
         <v>267</v>
@@ -1946,10 +1946,10 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>46.6</v>
+        <v>47</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>40.6</v>
+        <v>57.7</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1991,14 +1991,14 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>49</v>
+        <v>38.5</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2007,21 +2007,21 @@
         </is>
       </c>
       <c r="K25" s="3" t="n">
-        <v>42.1</v>
+        <v>54.5</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N25" s="3" t="n">
-        <v>42.1</v>
+        <v>36.4</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2041,25 +2041,25 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>50</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>43</v>
+        <v>38.4</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-D-N-U</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2068,21 +2068,21 @@
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>76.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>43.3</v>
+        <v>44.1</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>37.3</v>
+        <v>46.1</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>76.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>38.5</v>
+        <v>50</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2163,25 +2163,25 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>54.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>39.3</v>
+        <v>45.2</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-D</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2190,21 +2190,21 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>54.1</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>40.5</v>
+        <v>48.1</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>60.9</v>
+        <v>60.6</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -2235,14 +2235,14 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>46.4</v>
+        <v>36.4</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2251,21 +2251,21 @@
         </is>
       </c>
       <c r="K29" s="3" t="n">
-        <v>63</v>
+        <v>52.9</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>48.1</v>
+        <v>41.2</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2285,48 +2285,48 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>45.9</v>
+        <v>51.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>42.9</v>
+        <v>37.9</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-N-U</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>40</v>
+        <v>45.2</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>46.7</v>
+        <v>35.7</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2346,48 +2346,48 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>45.8</v>
+        <v>44.2</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>42.4</v>
+        <v>49.4</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K31" s="3" t="n">
         <v>50</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>50</v>
+        <v>68.2</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>46.9</v>
+        <v>43.8</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G32" s="3" t="n">
-        <v>46.9</v>
+        <v>43.8</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2434,21 +2434,21 @@
         </is>
       </c>
       <c r="K32" s="3" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N32" s="3" t="n">
-        <v>43.3</v>
+        <v>44.4</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33">
@@ -2459,19 +2459,19 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>38.1</v>
+        <v>35.3</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2479,37 +2479,37 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>47.6</v>
+        <v>44.1</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="K33" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N33" s="3" t="n">
         <v>50</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>36.9</v>
+        <v>43.2</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2540,14 +2540,14 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>44</v>
+        <v>42.4</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="K34" s="3" t="n">
-        <v>38.5</v>
+        <v>48</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>44.2</v>
+        <v>48</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2590,25 +2590,25 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>47.8</v>
+        <v>48.3</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>42.6</v>
+        <v>43.7</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2617,21 +2617,21 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>60</v>
+        <v>62.1</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>42.9</v>
+        <v>41.4</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>47.5</v>
+        <v>37</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>179</v>
+        <v>243</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2662,26 +2662,26 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>48.6</v>
+        <v>49.8</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>179</v>
+        <v>243</v>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K36" s="3" t="n">
-        <v>56.8</v>
+        <v>39.1</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>37</v>
+        <v>87</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
@@ -2689,10 +2689,10 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>54.1</v>
+        <v>50.6</v>
       </c>
       <c r="O36" s="4" t="n">
-        <v>37</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2712,45 +2712,45 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>45</v>
+        <v>50.8</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K37" s="3" t="n">
-        <v>38.6</v>
+        <v>45.5</v>
       </c>
       <c r="L37" s="4" t="n">
         <v>44</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>43.2</v>
+        <v>50</v>
       </c>
       <c r="O37" s="4" t="n">
         <v>44</v>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2773,25 +2773,25 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>35.1</v>
+        <v>39.2</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>41.8</v>
+        <v>39.2</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2800,21 +2800,21 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>44.8</v>
+        <v>37</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>48.3</v>
+        <v>42.6</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2834,25 +2834,25 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>73.8</v>
+        <v>70</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>42.6</v>
+        <v>38</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-D</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -2861,21 +2861,21 @@
         </is>
       </c>
       <c r="K39" s="3" t="n">
-        <v>77.3</v>
+        <v>93.3</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N39" s="3" t="n">
-        <v>36.4</v>
+        <v>46.7</v>
       </c>
       <c r="O39" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2895,10 +2895,10 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>74.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2906,14 +2906,14 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>46.9</v>
+        <v>39.2</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-D-N-U</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="K40" s="3" t="n">
-        <v>89.7</v>
+        <v>94.7</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="N40" s="3" t="n">
-        <v>62.1</v>
+        <v>47.4</v>
       </c>
       <c r="O40" s="4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>37.8</v>
+        <v>45.8</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2967,26 +2967,26 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>51.4</v>
+        <v>50</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-U</t>
+          <t>U-N-U-U</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>61.1</v>
+        <v>50</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>43</v>
+        <v>38.7</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -3028,26 +3028,26 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>41.7</v>
+        <v>45.1</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>58.3</v>
+        <v>40.8</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43">
@@ -3069,34 +3069,34 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>35.5</v>
+        <v>40.2</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>40.8</v>
+        <v>41.5</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>152</v>
+        <v>82</v>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -3105,21 +3105,21 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>50</v>
+        <v>41.4</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>42.3</v>
+        <v>44.8</v>
       </c>
       <c r="O43" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3139,45 +3139,45 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>37.3</v>
+        <v>36.2</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>188</v>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>D-D-U-U</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G44" s="3" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>185</v>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-U</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="K44" s="3" t="n">
-        <v>38.4</v>
+        <v>35.6</v>
       </c>
       <c r="L44" s="4" t="n">
         <v>73</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>45.2</v>
+        <v>46.6</v>
       </c>
       <c r="O44" s="4" t="n">
         <v>73</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3200,25 +3200,25 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>56.7</v>
+        <v>73</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>48.5</v>
+        <v>36.5</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>45.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>54.3</v>
+        <v>43.5</v>
       </c>
       <c r="O45" s="4" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="46">
@@ -3252,19 +3252,19 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>50</v>
+        <v>43.1</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -3272,14 +3272,14 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>48</v>
+        <v>48.3</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -3288,21 +3288,21 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>52.4</v>
+        <v>54.2</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>52.4</v>
+        <v>58.3</v>
       </c>
       <c r="O46" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3322,25 +3322,25 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>43.9</v>
+        <v>45.1</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>42.1</v>
+        <v>45.1</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>42.3</v>
+        <v>38.1</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>42.3</v>
+        <v>47.6</v>
       </c>
       <c r="O47" s="4" t="n">
-        <v>52</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3383,25 +3383,25 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>62.4</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>35.2</v>
+        <v>40</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3410,21 +3410,21 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>79.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>38.2</v>
+        <v>42.9</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3444,10 +3444,10 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>57.1</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3455,14 +3455,14 @@
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>38.6</v>
+        <v>40.7</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-D</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3471,21 +3471,21 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>76.2</v>
+        <v>53.1</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>38.1</v>
+        <v>40.6</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3505,25 +3505,25 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>71.09999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>40.8</v>
+        <v>48</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-D</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>82.8</v>
+        <v>63.6</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
@@ -3543,10 +3543,10 @@
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>37.9</v>
+        <v>54.5</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>80.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3577,14 +3577,14 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>45.1</v>
+        <v>44.2</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>N-N-N-U</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
@@ -3604,10 +3604,10 @@
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>42.9</v>
+        <v>36.4</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52">
@@ -3618,57 +3618,57 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>38.5</v>
+        <v>42.9</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>42.6</v>
+        <v>38.1</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="K52" s="3" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="L52" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="n">
         <v>40.4</v>
       </c>
-      <c r="L52" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N52" s="3" t="n">
-        <v>38.3</v>
-      </c>
       <c r="O52" s="4" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3688,25 +3688,25 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>60.3</v>
+        <v>62.1</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>41.2</v>
+        <v>36.2</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -3715,21 +3715,21 @@
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>53.3</v>
+        <v>56.2</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>43.3</v>
+        <v>43.8</v>
       </c>
       <c r="O53" s="4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54">
@@ -3740,19 +3740,19 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>41.6</v>
+        <v>38.4</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3760,37 +3760,37 @@
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>40.6</v>
+        <v>44.6</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>50</v>
+        <v>41.5</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="55">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3810,25 +3810,25 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>41.5</v>
+        <v>48</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>56.6</v>
+        <v>44</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -3837,21 +3837,21 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>38.5</v>
+        <v>46.7</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>46.2</v>
+        <v>46.7</v>
       </c>
       <c r="O55" s="4" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -4027,17 +4027,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -4049,45 +4049,45 @@
         <v>50</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>41.7</v>
+        <v>44.4</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-N</t>
+          <t>N-D-N-U</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M2" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -4098,56 +4098,56 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>D-U-U-U</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
           <t>D/U</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>31</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-U</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="M3" s="3" t="n">
-        <v>60</v>
+        <v>41.2</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -4155,10 +4155,10 @@
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>60</v>
+        <v>47.1</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -4169,64 +4169,64 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>53.3</v>
+        <v>38.1</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I4" s="3" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-U</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="n">
         <v>60</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-D</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>N/U</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>40</v>
       </c>
       <c r="N4" s="4" t="n">
         <v>5</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P4" s="3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q4" s="4" t="n">
         <v>5</v>
@@ -4240,44 +4240,44 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>53.8</v>
+        <v>43.5</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>69.2</v>
+        <v>39.1</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4286,21 +4286,21 @@
         </is>
       </c>
       <c r="M5" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P5" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -4311,17 +4311,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -4330,25 +4330,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>60</v>
+        <v>42.1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>40</v>
+        <v>47.4</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-D</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -4357,14 +4357,14 @@
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>4</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -4401,48 +4401,48 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>52.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>D-N-D-U</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="N7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I7" s="3" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>N-D-N-D</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="P7" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -4453,17 +4453,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -4472,48 +4472,48 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>61.5</v>
+        <v>47.4</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>38.5</v>
+        <v>47.4</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-D</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M8" s="3" t="n">
-        <v>33.3</v>
+        <v>75</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -4524,29 +4524,29 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>33.3</v>
+        <v>46.7</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -4554,26 +4554,26 @@
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>58.3</v>
+        <v>53.3</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -4581,10 +4581,10 @@
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>83.3</v>
+        <v>57.1</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -4595,49 +4595,49 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>N-U-D-D</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>N-N-U-D</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
         </is>
       </c>
       <c r="M10" s="3" t="n">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
@@ -4666,44 +4666,44 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>53.8</v>
+        <v>43.8</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>53.8</v>
+        <v>43.8</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4712,21 +4712,21 @@
         </is>
       </c>
       <c r="M11" s="3" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P11" s="3" t="n">
-        <v>40</v>
+        <v>57.1</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -4737,44 +4737,44 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>45.5</v>
+        <v>66.7</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>45.5</v>
+        <v>42.9</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -4783,10 +4783,10 @@
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="P12" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -4808,17 +4808,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -4827,48 +4827,48 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>53.8</v>
+        <v>75</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>46.2</v>
+        <v>58.3</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M13" s="3" t="n">
-        <v>44.4</v>
+        <v>83.3</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P13" s="3" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -4879,29 +4879,29 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>50</v>
+        <v>52.4</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -4909,26 +4909,26 @@
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>50</v>
+        <v>52.4</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -4950,17 +4950,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -4969,25 +4969,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>70.8</v>
+        <v>62.5</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>24</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>33.3</v>
+        <v>41.7</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -4996,21 +4996,21 @@
         </is>
       </c>
       <c r="M15" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>44.4</v>
+        <v>37.5</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -5021,17 +5021,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -5040,48 +5040,48 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>47.4</v>
+        <v>45.8</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-U</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I16" s="3" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-D</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="M16" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -5092,17 +5092,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -5111,25 +5111,25 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>38.9</v>
+        <v>40.7</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>44.4</v>
+        <v>40.7</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-U</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P17" s="3" t="n">
@@ -5163,67 +5163,67 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>44.8</v>
+        <v>40.9</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>41.4</v>
+        <v>59.1</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M18" s="3" t="n">
-        <v>46.2</v>
+        <v>44.4</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P18" s="3" t="n">
-        <v>38.5</v>
+        <v>66.7</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -5234,29 +5234,29 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>45.8</v>
+        <v>50</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
@@ -5264,26 +5264,26 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>54.2</v>
+        <v>45.5</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M19" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -5291,10 +5291,10 @@
         </is>
       </c>
       <c r="P19" s="3" t="n">
-        <v>42.9</v>
+        <v>41.7</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -5305,64 +5305,64 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>41.7</v>
+        <v>48.1</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>D-D-D-U</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>42.9</v>
+        <v>57.1</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>7</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>57.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>7</v>
@@ -5376,67 +5376,67 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-D</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>D-D-U-D</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="M21" s="3" t="n">
-        <v>54.5</v>
+        <v>46.2</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P21" s="3" t="n">
-        <v>63.6</v>
+        <v>46.2</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -5447,17 +5447,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -5466,10 +5466,10 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>59.3</v>
+        <v>62.5</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
@@ -5477,14 +5477,14 @@
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>48.1</v>
+        <v>45.8</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="M22" s="3" t="n">
-        <v>63.6</v>
+        <v>58.3</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -5504,10 +5504,10 @@
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>54.5</v>
+        <v>58.3</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -5518,67 +5518,67 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="I23" s="3" t="n">
-        <v>57.1</v>
+        <v>53.8</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>D-N-U-U</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M23" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P23" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -5608,10 +5608,10 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>89.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -5619,10 +5619,10 @@
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>46.9</v>
+        <v>56.4</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
@@ -5660,17 +5660,17 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -5679,48 +5679,48 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>55</v>
+        <v>57.1</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-N</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="J25" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>U-D-U-D</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
       <c r="N25" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P25" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -5731,17 +5731,17 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -5750,10 +5750,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>70</v>
+        <v>61.1</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
@@ -5761,14 +5761,14 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>45</v>
+        <v>44.4</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-D-N-U</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -5777,21 +5777,21 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>83.3</v>
+        <v>75</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P26" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -5802,17 +5802,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -5821,25 +5821,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>62.5</v>
+        <v>40</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -5848,10 +5848,10 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="P27" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -5873,17 +5873,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -5892,10 +5892,10 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>64.7</v>
+        <v>54.5</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -5903,26 +5903,26 @@
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>58.8</v>
+        <v>45.5</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-D</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -5930,10 +5930,10 @@
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -5944,17 +5944,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>53.3</v>
+        <v>53.8</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -5974,37 +5974,37 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-N</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>D/N</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="J29" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>N-U-D-D</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
       <c r="N29" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>42.9</v>
+        <v>60</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -6015,67 +6015,67 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>42.9</v>
+        <v>45</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>61.9</v>
+        <v>50</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-N-U</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>75</v>
+        <v>46.2</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>62.5</v>
+        <v>53.8</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
@@ -6086,17 +6086,17 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>D-N-D</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -6105,48 +6105,48 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>54.5</v>
+        <v>52.6</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>36.4</v>
+        <v>52.6</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-D</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M31" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P31" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -6157,17 +6157,17 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -6176,10 +6176,10 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>46.7</v>
+        <v>41.2</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -6187,37 +6187,37 @@
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>46.7</v>
+        <v>47.1</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -6228,67 +6228,67 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>D-N-N-U</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="N33" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J33" s="4" t="n">
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q33" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>N-D-N-N</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q33" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -6299,17 +6299,17 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -6318,48 +6318,48 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>41.9</v>
+        <v>40.9</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>48.4</v>
+        <v>50</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N34" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="M34" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N34" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="P34" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
@@ -6370,17 +6370,17 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -6389,10 +6389,10 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>43.5</v>
+        <v>52.6</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -6400,26 +6400,26 @@
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>47.8</v>
+        <v>42.1</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M35" s="3" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -6441,67 +6441,67 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>55.9</v>
+        <v>43.2</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>64.7</v>
+        <v>43.2</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-U</t>
+          <t>D-U-U-U</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>80</v>
+        <v>52.4</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P36" s="3" t="n">
-        <v>60</v>
+        <v>47.6</v>
       </c>
       <c r="Q36" s="4" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37">
@@ -6512,17 +6512,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -6531,10 +6531,10 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>51.5</v>
+        <v>45.8</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
@@ -6542,37 +6542,37 @@
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>42.4</v>
+        <v>41.7</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-U</t>
+          <t>D-D-U-U</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M37" s="3" t="n">
-        <v>38.5</v>
+        <v>40</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P37" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="Q37" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
@@ -6583,44 +6583,44 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>50</v>
+        <v>42.9</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>40.9</v>
+        <v>39.3</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-D</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -6629,21 +6629,21 @@
         </is>
       </c>
       <c r="M38" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
@@ -6654,17 +6654,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>N-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -6673,25 +6673,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>66.7</v>
+        <v>77.8</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>9</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>55.6</v>
+        <v>66.7</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-D</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -6700,21 +6700,21 @@
         </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P39" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q39" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -6725,17 +6725,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -6744,25 +6744,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>47.6</v>
+        <v>50</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-D-N-U</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="M40" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -6782,10 +6782,10 @@
         </is>
       </c>
       <c r="P40" s="3" t="n">
-        <v>77.8</v>
+        <v>50</v>
       </c>
       <c r="Q40" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -6796,67 +6796,67 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>42.9</v>
+        <v>60</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-U</t>
+          <t>U-N-U-U</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M41" s="3" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P41" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -6867,17 +6867,17 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -6886,10 +6886,10 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>40.7</v>
+        <v>45.9</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -6897,14 +6897,14 @@
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>51.9</v>
+        <v>45.9</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
@@ -6913,10 +6913,10 @@
         </is>
       </c>
       <c r="M42" s="3" t="n">
-        <v>45.5</v>
+        <v>42.9</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -6924,10 +6924,10 @@
         </is>
       </c>
       <c r="P42" s="3" t="n">
-        <v>81.8</v>
+        <v>50</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43">
@@ -6938,29 +6938,29 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>48</v>
+        <v>46.2</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -6968,14 +6968,14 @@
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>44</v>
+        <v>53.8</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -6984,21 +6984,21 @@
         </is>
       </c>
       <c r="M43" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P43" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q43" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -7009,67 +7009,67 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>D/U</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>D-D-U-U</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
           <t>D</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>43.8</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="J44" s="4" t="n">
-        <v>32</v>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-U</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
         </is>
       </c>
       <c r="M44" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P44" s="3" t="n">
-        <v>41.7</v>
+        <v>62.5</v>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -7080,17 +7080,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7099,48 +7099,48 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>52.4</v>
+        <v>72.2</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>47.6</v>
+        <v>44.4</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-D</t>
+          <t>U-U-D-D</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M45" s="3" t="n">
-        <v>41.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P45" s="3" t="n">
-        <v>50</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -7151,67 +7151,67 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>75</v>
+        <v>38.5</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>37.5</v>
+        <v>46.2</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M46" s="3" t="n">
-        <v>75</v>
+        <v>66.7</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P46" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q46" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -7222,29 +7222,29 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>48.1</v>
+        <v>53.3</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
@@ -7252,26 +7252,26 @@
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>51.9</v>
+        <v>40</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M47" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="P47" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="Q47" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -7293,17 +7293,17 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -7312,10 +7312,10 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>70</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -7323,14 +7323,14 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>40</v>
+        <v>41.2</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>U-D-N-U</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -7339,21 +7339,21 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>62.5</v>
+        <v>66.7</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -7364,17 +7364,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -7383,34 +7383,34 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>75</v>
+        <v>53.3</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
+          <t>D/N/U</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="J49" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>U-N-D-N</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
           <t>D/N</t>
         </is>
       </c>
-      <c r="I49" s="3" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="J49" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>U-U-N-D</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="M49" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N49" s="4" t="n">
         <v>6</v>
@@ -7435,56 +7435,56 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>U-N-D</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>62.5</v>
+        <v>45.5</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>U-U-N-D</t>
+          <t>U-N-D-D</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M50" s="3" t="n">
-        <v>85.7</v>
+        <v>66.7</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="P50" s="3" t="n">
-        <v>42.9</v>
+        <v>66.7</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -7506,17 +7506,17 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -7525,25 +7525,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>87.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>37.5</v>
+        <v>57.1</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>N-N-N-U</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -7552,14 +7552,14 @@
         </is>
       </c>
       <c r="M51" s="3" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="N51" s="4" t="n">
         <v>3</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P51" s="3" t="n">
@@ -7577,29 +7577,29 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>40</v>
+        <v>36.8</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -7607,37 +7607,37 @@
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>36</v>
+        <v>36.8</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>54.5</v>
+        <v>33.3</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>45.5</v>
+        <v>50</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
@@ -7648,17 +7648,17 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -7667,48 +7667,48 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>53.8</v>
+        <v>68.8</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>46.2</v>
+        <v>37.5</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M53" s="3" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P53" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q53" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -7719,67 +7719,67 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>U-D-D</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
         </is>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="G54" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="I54" s="3" t="n">
-        <v>40</v>
+        <v>35.3</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>N-D-U-D</t>
+          <t>D-U-D-D</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M54" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P54" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q54" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -7790,67 +7790,67 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Çarşamba</t>
+          <t>Perşembe</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Perşembe</t>
+          <t>Cuma</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-N-U</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>41.7</v>
+        <v>36.8</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I55" s="3" t="n">
-        <v>50</v>
+        <v>47.4</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>D-D-N-U</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M55" s="3" t="n">
         <v>50</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P55" s="3" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="Q55" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/BIS_usa.xlsx
+++ b/BIS_usa.xlsx
@@ -873,7 +873,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -882,25 +882,25 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>55.3</v>
+        <v>56.3</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G7" s="3" t="n">
-        <v>47.9</v>
+        <v>43.7</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="K7" s="3" t="n">
-        <v>48.6</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="N7" s="3" t="n">
-        <v>51.4</v>
+        <v>52.6</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -934,7 +934,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -943,10 +943,10 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>49.4</v>
+        <v>40.4</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -954,26 +954,26 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>37.3</v>
+        <v>40.4</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>52</v>
+        <v>44.4</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1065,25 +1065,25 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>40.3</v>
+        <v>44.1</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G10" s="3" t="n">
-        <v>43.4</v>
+        <v>41.9</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1092,21 +1092,21 @@
         </is>
       </c>
       <c r="K10" s="3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N10" s="3" t="n">
-        <v>34.6</v>
+        <v>41.7</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>61.5</v>
+        <v>55.2</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
         </is>
       </c>
       <c r="G13" s="3" t="n">
-        <v>39.7</v>
+        <v>37.1</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-D</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1275,21 +1275,21 @@
         </is>
       </c>
       <c r="K13" s="3" t="n">
-        <v>58.3</v>
+        <v>54.1</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N13" s="3" t="n">
-        <v>37.5</v>
+        <v>43.2</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1309,48 +1309,48 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>42.6</v>
+        <v>52.1</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G14" s="3" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>D-U-D-N</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="n">
         <v>45.5</v>
       </c>
-      <c r="H14" s="4" t="n">
-        <v>101</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>D-U-D-D</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>38.7</v>
-      </c>
       <c r="L14" s="4" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N14" s="3" t="n">
-        <v>54.8</v>
+        <v>40.9</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>49.7</v>
+        <v>55.4</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1503,14 +1503,14 @@
         </is>
       </c>
       <c r="G17" s="3" t="n">
-        <v>42.1</v>
+        <v>43.4</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="K17" s="3" t="n">
-        <v>47.2</v>
+        <v>60</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="N17" s="3" t="n">
-        <v>47.2</v>
+        <v>42.9</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1797,25 +1797,25 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>53.6</v>
+        <v>56.1</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G22" s="3" t="n">
-        <v>43.6</v>
+        <v>40.9</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1824,21 +1824,21 @@
         </is>
       </c>
       <c r="K22" s="3" t="n">
-        <v>47.9</v>
+        <v>50</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N22" s="3" t="n">
-        <v>45.8</v>
+        <v>42.3</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1919,10 +1919,10 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>82.8</v>
+        <v>81.8</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>267</v>
+        <v>143</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1930,14 +1930,14 @@
         </is>
       </c>
       <c r="G24" s="3" t="n">
-        <v>50.6</v>
+        <v>44.8</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>267</v>
+        <v>143</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-U</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1946,10 +1946,10 @@
         </is>
       </c>
       <c r="K24" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>47</v>
+        <v>47.1</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>134</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>48.3</v>
+        <v>46.5</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2601,14 +2601,14 @@
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>43.7</v>
+        <v>44.6</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2617,10 +2617,10 @@
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>62.1</v>
+        <v>45.9</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
@@ -2628,10 +2628,10 @@
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>41.4</v>
+        <v>45.9</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="36">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>39.2</v>
+        <v>50</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2784,14 +2784,14 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>39.2</v>
+        <v>38.3</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2800,21 +2800,21 @@
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>37</v>
+        <v>45.8</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>42.6</v>
+        <v>45.8</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3383,25 +3383,25 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>62.4</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>40</v>
+        <v>39.1</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3410,21 +3410,21 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>64.3</v>
+        <v>62.1</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>42.9</v>
+        <v>48.3</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3627,10 +3627,10 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>42.9</v>
+        <v>61.4</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3638,37 +3638,37 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>38.1</v>
+        <v>42.2</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>34.6</v>
+        <v>75.8</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>40.4</v>
+        <v>42.4</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53">
@@ -3740,57 +3740,57 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>38.4</v>
+        <v>46.4</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>44.6</v>
+        <v>43.5</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>41.5</v>
+        <v>57.1</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>39</v>
+        <v>52.4</v>
       </c>
       <c r="O54" s="4" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -4401,25 +4401,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>42.9</v>
+        <v>44.4</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -4428,21 +4428,21 @@
         </is>
       </c>
       <c r="M7" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P7" s="3" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4463,57 +4463,57 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>47.4</v>
+        <v>33.3</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>47.4</v>
+        <v>44.4</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="M8" s="3" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -4605,34 +4605,34 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>46.7</v>
+        <v>56.2</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>46.7</v>
+        <v>37.5</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>N-U-D-D</t>
+          <t>N-U-D-N</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -4644,18 +4644,18 @@
         <v>50</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P10" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -4827,48 +4827,48 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>75</v>
+        <v>48.5</v>
       </c>
       <c r="G13" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-D</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="N13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>58.3</v>
-      </c>
-      <c r="J13" s="4" t="n">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="Q13" s="4" t="n">
         <v>12</v>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-N</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="Q13" s="4" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -4889,57 +4889,57 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>52.4</v>
+        <v>58.8</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>52.4</v>
+        <v>35.3</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>40.7</v>
+        <v>61.5</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
@@ -5122,26 +5122,26 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>40.7</v>
+        <v>53.8</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-U</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M17" s="3" t="n">
-        <v>33.3</v>
+        <v>85.7</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -5149,10 +5149,10 @@
         </is>
       </c>
       <c r="P17" s="3" t="n">
-        <v>66.7</v>
+        <v>57.1</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>D-D-U</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -5466,25 +5466,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>62.5</v>
+        <v>63.6</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-U</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -5493,21 +5493,21 @@
         </is>
       </c>
       <c r="M22" s="3" t="n">
-        <v>58.3</v>
+        <v>80</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P22" s="3" t="n">
-        <v>58.3</v>
+        <v>40</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -5608,7 +5608,7 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>84.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G24" s="4" t="n">
         <v>39</v>
@@ -5619,14 +5619,14 @@
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>56.4</v>
+        <v>46.2</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-N</t>
+          <t>N-N-N-U</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="M24" s="3" t="n">
-        <v>83.3</v>
+        <v>94.7</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="P24" s="3" t="n">
-        <v>50</v>
+        <v>42.1</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-U</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -6389,25 +6389,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>52.6</v>
+        <v>44.4</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>42.1</v>
+        <v>38.9</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-N</t>
+          <t>U-D-D-U</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -6416,21 +6416,21 @@
         </is>
       </c>
       <c r="M35" s="3" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -6602,25 +6602,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>39.3</v>
+        <v>41.7</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>U-U-D-D</t>
+          <t>U-U-D-N</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -6629,10 +6629,10 @@
         </is>
       </c>
       <c r="M38" s="3" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="P38" s="3" t="n">
-        <v>55.6</v>
+        <v>80</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -7312,45 +7312,45 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>70.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>41.2</v>
+        <v>64.3</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>U-D-N-U</t>
+          <t>U-D-N-N</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N48" s="4" t="n">
         <v>6</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="Q48" s="4" t="n">
         <v>6</v>
@@ -7587,57 +7587,57 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>U-D-U</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>36.8</v>
+        <v>75</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>36.8</v>
+        <v>37.5</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-U</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>D/N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>33.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>50</v>
+        <v>44.4</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -7738,45 +7738,45 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>41.2</v>
+        <v>50</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>35.3</v>
+        <v>37.5</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M54" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="N54" s="4" t="n">
         <v>4</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P54" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q54" s="4" t="n">
         <v>4</v>

--- a/BIS_usa.xlsx
+++ b/BIS_usa.xlsx
@@ -1422,7 +1422,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>66.7</v>
+        <v>59.8</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1442,14 +1442,14 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1458,10 +1458,10 @@
         </is>
       </c>
       <c r="K16" s="3" t="n">
-        <v>57.6</v>
+        <v>53.8</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>39.4</v>
+        <v>53.8</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>79.8</v>
+        <v>64.2</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1686,14 +1686,14 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>41.4</v>
+        <v>36.8</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1702,21 +1702,21 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>78.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>43.2</v>
+        <v>51.7</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
@@ -2032,19 +2032,19 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>43.8</v>
+        <v>35.9</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -2052,26 +2052,26 @@
         </is>
       </c>
       <c r="G26" s="3" t="n">
-        <v>48.4</v>
+        <v>39.3</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K26" s="3" t="n">
-        <v>48.1</v>
+        <v>39.5</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="N26" s="3" t="n">
-        <v>48.1</v>
+        <v>48.8</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>46.2</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -2113,14 +2113,14 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>37.3</v>
+        <v>34.9</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2129,21 +2129,21 @@
         </is>
       </c>
       <c r="K27" s="3" t="n">
-        <v>52</v>
+        <v>44.9</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>48</v>
+        <v>38.8</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2285,25 +2285,25 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>35.9</v>
+        <v>44.9</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2312,21 +2312,21 @@
         </is>
       </c>
       <c r="K30" s="3" t="n">
-        <v>59.5</v>
+        <v>61.5</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N30" s="3" t="n">
-        <v>42.9</v>
+        <v>46.2</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2956,48 +2956,48 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>77.7</v>
+        <v>52.1</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>37.9</v>
+        <v>35.6</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K41" s="3" t="n">
-        <v>70.8</v>
+        <v>41.4</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>37.5</v>
+        <v>41.4</v>
       </c>
       <c r="O41" s="4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="42">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>68.8</v>
+        <v>80.3</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -3150,14 +3150,14 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>41.7</v>
+        <v>52.8</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-U</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
@@ -3177,10 +3177,10 @@
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>49.1</v>
+        <v>57.1</v>
       </c>
       <c r="O44" s="4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="45">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3200,10 +3200,10 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>75.2</v>
+        <v>62.1</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -3211,14 +3211,14 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>44.4</v>
+        <v>39.8</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -3227,18 +3227,18 @@
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="L45" s="4" t="n">
         <v>25</v>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="O45" s="4" t="n">
         <v>25</v>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3383,10 +3383,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>85.7</v>
+        <v>78.7</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>287</v>
+        <v>127</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -3394,14 +3394,14 @@
         </is>
       </c>
       <c r="G48" s="3" t="n">
-        <v>56.1</v>
+        <v>42.5</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>287</v>
+        <v>127</v>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>79.3</v>
+        <v>81.5</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>48.3</v>
+        <v>48.1</v>
       </c>
       <c r="O48" s="4" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3444,25 +3444,25 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>66.2</v>
+        <v>55.6</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G49" s="3" t="n">
-        <v>45.5</v>
+        <v>47.2</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -3471,21 +3471,21 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>76.7</v>
+        <v>55.2</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>43.3</v>
+        <v>44.8</v>
       </c>
       <c r="O49" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3505,10 +3505,10 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>67.7</v>
+        <v>75.3</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3516,14 +3516,14 @@
         </is>
       </c>
       <c r="G50" s="3" t="n">
-        <v>38.5</v>
+        <v>39.2</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -3532,21 +3532,21 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>75</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>43.5</v>
+        <v>42.9</v>
       </c>
       <c r="O50" s="4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3566,25 +3566,25 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>39.1</v>
+        <v>33.7</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
@@ -3604,10 +3604,10 @@
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>42.9</v>
+        <v>41.7</v>
       </c>
       <c r="O51" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3627,25 +3627,25 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>59.4</v>
+        <v>61.5</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>42.2</v>
+        <v>38.5</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -3654,21 +3654,21 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>46.4</v>
+        <v>37.5</v>
       </c>
       <c r="O52" s="4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4237,37 +4237,37 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>56.6</v>
+        <v>43.9</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G62" s="3" t="n">
-        <v>41</v>
+        <v>37.4</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K62" s="3" t="n">
-        <v>48.3</v>
+        <v>37.5</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="N62" s="3" t="n">
-        <v>41.4</v>
+        <v>45</v>
       </c>
       <c r="O62" s="4" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4420,37 +4420,37 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>42.7</v>
+        <v>43.4</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G65" s="3" t="n">
-        <v>39.7</v>
+        <v>45.8</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>131</v>
+        <v>83</v>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K65" s="3" t="n">
-        <v>47.8</v>
+        <v>57.1</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
@@ -4458,10 +4458,10 @@
         </is>
       </c>
       <c r="N65" s="3" t="n">
-        <v>39.1</v>
+        <v>65.7</v>
       </c>
       <c r="O65" s="4" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="66">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -5091,25 +5091,25 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G76" s="3" t="n">
-        <v>35.4</v>
+        <v>37.1</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -5118,21 +5118,21 @@
         </is>
       </c>
       <c r="K76" s="3" t="n">
-        <v>45.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>41.9</v>
+        <v>43.8</v>
       </c>
       <c r="O76" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77">
@@ -5326,34 +5326,34 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>47.3</v>
+        <v>37.6</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G80" s="3" t="n">
-        <v>40</v>
+        <v>48.2</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -5362,21 +5362,21 @@
         </is>
       </c>
       <c r="K80" s="3" t="n">
-        <v>47.6</v>
+        <v>40.5</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N80" s="3" t="n">
-        <v>52.4</v>
+        <v>43.2</v>
       </c>
       <c r="O80" s="4" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="81">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>41.4</v>
+        <v>58.9</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -5529,14 +5529,14 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>35.7</v>
+        <v>50.7</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>U-D-D-D</t>
+          <t>U-D-D-N</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c r="K83" s="3" t="n">
-        <v>48</v>
+        <v>61.5</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="N83" s="3" t="n">
-        <v>44</v>
+        <v>46.2</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -5579,10 +5579,10 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>66.3</v>
+        <v>76.5</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -5590,14 +5590,14 @@
         </is>
       </c>
       <c r="G84" s="3" t="n">
-        <v>34.9</v>
+        <v>38.8</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -5606,21 +5606,21 @@
         </is>
       </c>
       <c r="K84" s="3" t="n">
-        <v>62.1</v>
+        <v>76</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N84" s="3" t="n">
-        <v>44.8</v>
+        <v>40</v>
       </c>
       <c r="O84" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85">
@@ -5875,19 +5875,19 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>36.4</v>
+        <v>36.8</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5895,37 +5895,37 @@
         </is>
       </c>
       <c r="G89" s="3" t="n">
-        <v>49.1</v>
+        <v>52.6</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="K89" s="3" t="n">
-        <v>38.1</v>
+        <v>33.3</v>
       </c>
       <c r="L89" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N89" s="3" t="n">
-        <v>47.6</v>
+        <v>66.7</v>
       </c>
       <c r="O89" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -5945,10 +5945,10 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>67.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5956,14 +5956,14 @@
         </is>
       </c>
       <c r="G90" s="3" t="n">
-        <v>39.7</v>
+        <v>48.6</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-D</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -5972,21 +5972,21 @@
         </is>
       </c>
       <c r="K90" s="3" t="n">
-        <v>67.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="L90" s="4" t="n">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N90" s="3" t="n">
-        <v>41.2</v>
+        <v>36.2</v>
       </c>
       <c r="O90" s="4" t="n">
-        <v>34</v>
+        <v>69</v>
       </c>
     </row>
     <row r="91">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -6189,25 +6189,25 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G94" s="3" t="n">
-        <v>46.4</v>
+        <v>40.5</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -6216,21 +6216,21 @@
         </is>
       </c>
       <c r="K94" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="L94" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N94" s="3" t="n">
-        <v>43.8</v>
+        <v>52.4</v>
       </c>
       <c r="O94" s="4" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -7724,7 +7724,7 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="G16" s="4" t="n">
         <v>24</v>
@@ -7735,14 +7735,14 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>41.7</v>
+        <v>45.8</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -7754,18 +7754,18 @@
         <v>66.7</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P16" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8008,25 +8008,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>76.2</v>
+        <v>65</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -8035,21 +8035,21 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -8425,57 +8425,57 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>N/U</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="n">
         <v>42.9</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="N26" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>71.40000000000001</v>
-      </c>
-      <c r="J26" s="4" t="n">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="Q26" s="4" t="n">
         <v>7</v>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N26" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="Q26" s="4" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -8505,10 +8505,10 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>46.2</v>
+        <v>48</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -8516,37 +8516,37 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>53.8</v>
+        <v>40</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
           <t>N/U</t>
         </is>
       </c>
-      <c r="M27" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="N27" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
       <c r="P27" s="3" t="n">
-        <v>66.7</v>
+        <v>35.3</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -8718,25 +8718,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>70</v>
+        <v>66.7</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>35</v>
+        <v>37.5</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>D-U-N-U</t>
+          <t>D-U-N-N</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -8745,10 +8745,10 @@
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -8756,10 +8756,10 @@
         </is>
       </c>
       <c r="P30" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -9499,25 +9499,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>73.3</v>
+        <v>60</v>
       </c>
       <c r="G41" s="4" t="n">
         <v>15</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>53.3</v>
+        <v>40</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-U</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -9526,21 +9526,21 @@
         </is>
       </c>
       <c r="M41" s="3" t="n">
-        <v>60</v>
+        <v>42.9</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P41" s="3" t="n">
-        <v>80</v>
+        <v>42.9</v>
       </c>
       <c r="Q41" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>U-N-U</t>
+          <t>U-N-N</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9712,25 +9712,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>68.8</v>
+        <v>75</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>43.8</v>
+        <v>46.4</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-U</t>
+          <t>N-U-N-N</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -9739,21 +9739,21 @@
         </is>
       </c>
       <c r="M44" s="3" t="n">
-        <v>60</v>
+        <v>72.2</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P44" s="3" t="n">
-        <v>40</v>
+        <v>61.1</v>
       </c>
       <c r="Q44" s="4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9783,48 +9783,48 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>65.5</v>
+        <v>46.2</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>37.9</v>
+        <v>46.2</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-U</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M45" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P45" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="Q45" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -10007,14 +10007,14 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>50.9</v>
+        <v>46.2</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
@@ -10023,21 +10023,21 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>85.7</v>
+        <v>60</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>42.9</v>
+        <v>40</v>
       </c>
       <c r="Q48" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -10058,34 +10058,34 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>90.90000000000001</v>
+        <v>50</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>63.6</v>
+        <v>62.5</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -10094,21 +10094,21 @@
         </is>
       </c>
       <c r="M49" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="N49" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="N49" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O49" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="P49" s="3" t="n">
-        <v>60</v>
-      </c>
       <c r="Q49" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>U-N-N</t>
+          <t>U-N-U</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -10138,25 +10138,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>80</v>
+        <v>57.9</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>53.3</v>
+        <v>42.1</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>N-U-N-N</t>
+          <t>N-U-N-U</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -10165,21 +10165,21 @@
         </is>
       </c>
       <c r="M50" s="3" t="n">
-        <v>100</v>
+        <v>55.6</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P50" s="3" t="n">
-        <v>50</v>
+        <v>55.6</v>
       </c>
       <c r="Q50" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -10209,14 +10209,14 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>58.3</v>
+        <v>83.3</v>
       </c>
       <c r="G51" s="4" t="n">
         <v>12</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
@@ -10227,30 +10227,30 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>U-N-D-U</t>
+          <t>U-N-D-N</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M51" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P51" s="3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="Q51" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -10280,25 +10280,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>41.7</v>
+        <v>50</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-N</t>
+          <t>N-N-D-D</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -10307,21 +10307,21 @@
         </is>
       </c>
       <c r="M52" s="3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P52" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -10981,19 +10981,19 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>U-D-N</t>
+          <t>U-D-U</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
@@ -11001,26 +11001,26 @@
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>56.2</v>
+        <v>38.5</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-N</t>
+          <t>D-U-D-U</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M62" s="3" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -11028,10 +11028,10 @@
         </is>
       </c>
       <c r="P62" s="3" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="Q62" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>U-D-D</t>
+          <t>U-D-N</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -11203,48 +11203,48 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I65" s="3" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>D-U-D-D</t>
+          <t>D-U-D-N</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M65" s="3" t="n">
-        <v>54.5</v>
+        <v>40</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P65" s="3" t="n">
-        <v>36.4</v>
+        <v>80</v>
       </c>
       <c r="Q65" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -11975,7 +11975,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -11984,48 +11984,48 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>64.3</v>
+        <v>50</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>42.9</v>
+        <v>44.4</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M76" s="3" t="n">
-        <v>42.9</v>
+        <v>60</v>
       </c>
       <c r="N76" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P76" s="3" t="n">
-        <v>57.1</v>
+        <v>40</v>
       </c>
       <c r="Q76" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -12259,57 +12259,57 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-U</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>37.5</v>
+        <v>56.2</v>
       </c>
       <c r="G80" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="J80" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>D-N-D-U</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="N80" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I80" s="3" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="J80" s="4" t="n">
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q80" s="4" t="n">
         <v>8</v>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>D-N-D-N</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="M80" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="N80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O80" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="P80" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q80" s="4" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -12472,57 +12472,57 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>D-D-D</t>
+          <t>D-D-N</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>42.9</v>
+        <v>63.6</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="J83" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>U-D-D-N</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="N83" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I83" s="3" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="J83" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>U-D-D-D</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M83" s="3" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="N83" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="O83" s="2" t="inlineStr">
-        <is>
-          <t>D/U</t>
-        </is>
-      </c>
       <c r="P83" s="3" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="Q83" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -12552,25 +12552,25 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>69.2</v>
+        <v>85</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I84" s="3" t="n">
-        <v>46.2</v>
+        <v>45</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
@@ -12579,21 +12579,21 @@
         </is>
       </c>
       <c r="M84" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="N84" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P84" s="3" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="Q84" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -12910,45 +12910,45 @@
         <v>50</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I89" s="3" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-U</t>
+          <t>D-N-D-N</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M89" s="3" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="N89" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P89" s="3" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="Q89" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -12969,7 +12969,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>N-N-D</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -12978,10 +12978,10 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -12989,14 +12989,14 @@
         </is>
       </c>
       <c r="I90" s="3" t="n">
-        <v>55.6</v>
+        <v>45.8</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>N-N-N-D</t>
+          <t>N-N-N-N</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -13005,21 +13005,21 @@
         </is>
       </c>
       <c r="M90" s="3" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="N90" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="P90" s="3" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="Q90" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="91">
@@ -13253,7 +13253,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -13262,25 +13262,25 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>81</v>
+        <v>61.1</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I94" s="3" t="n">
-        <v>42.9</v>
+        <v>38.9</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-N</t>
+          <t>D-D-N-D</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -13289,21 +13289,21 @@
         </is>
       </c>
       <c r="M94" s="3" t="n">
-        <v>83.3</v>
+        <v>50</v>
       </c>
       <c r="N94" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P94" s="3" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="Q94" s="4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="95">

--- a/BIS_usa.xlsx
+++ b/BIS_usa.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -577,25 +577,25 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>62.1</v>
+        <v>65.2</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G2" s="3" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -604,21 +604,21 @@
         </is>
       </c>
       <c r="K2" s="3" t="n">
-        <v>71.8</v>
+        <v>69</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="N2" s="3" t="n">
-        <v>35.9</v>
+        <v>34.5</v>
       </c>
       <c r="O2" s="4" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>84.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -649,14 +649,14 @@
         </is>
       </c>
       <c r="G3" s="3" t="n">
-        <v>40.4</v>
+        <v>48.2</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-U</t>
+          <t>U-N-N-N</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="K3" s="3" t="n">
-        <v>85.7</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="N3" s="3" t="n">
-        <v>45.2</v>
+        <v>48.6</v>
       </c>
       <c r="O3" s="4" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -812,7 +812,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -821,25 +821,25 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>56.8</v>
+        <v>44.4</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G6" s="3" t="n">
-        <v>44.2</v>
+        <v>37.1</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -848,21 +848,21 @@
         </is>
       </c>
       <c r="K6" s="3" t="n">
-        <v>66.7</v>
+        <v>44.8</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>50</v>
+        <v>37.9</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>80.2</v>
+        <v>80.8</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>177</v>
@@ -934,19 +934,19 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>41</v>
+        <v>38.2</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -954,26 +954,26 @@
         </is>
       </c>
       <c r="G8" s="3" t="n">
-        <v>44.8</v>
+        <v>38.2</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K8" s="3" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>45.8</v>
+        <v>48</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -995,7 +995,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1004,48 +1004,48 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-U</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="n">
         <v>42.7</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="O9" s="4" t="n">
         <v>82</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>82</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-N</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>36</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="O9" s="4" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -1300,57 +1300,57 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>35.5</v>
+        <v>35.1</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-U</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G14" s="3" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>93</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-N</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>37</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="N14" s="3" t="n">
-        <v>35.1</v>
+        <v>39.7</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>37</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1370,48 +1370,48 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>43.9</v>
+        <v>43.6</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G15" s="3" t="n">
-        <v>39.3</v>
+        <v>39.9</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K15" s="3" t="n">
-        <v>39</v>
+        <v>48.2</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N15" s="3" t="n">
-        <v>36.6</v>
+        <v>42.9</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>75.3</v>
+        <v>65.3</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1686,14 +1686,14 @@
         </is>
       </c>
       <c r="G20" s="3" t="n">
-        <v>38.1</v>
+        <v>34.7</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1702,21 +1702,21 @@
         </is>
       </c>
       <c r="K20" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>40</v>
+        <v>44.8</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2163,10 +2163,10 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>61.5</v>
+        <v>56.5</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -2174,14 +2174,14 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>39.7</v>
+        <v>38.9</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2190,21 +2190,21 @@
         </is>
       </c>
       <c r="K28" s="3" t="n">
-        <v>58.6</v>
+        <v>56.1</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="N28" s="3" t="n">
-        <v>37.9</v>
+        <v>34.1</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2224,48 +2224,48 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>N-D-D-D</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="E29" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>72</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>N-D-D-N</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>43.8</v>
-      </c>
       <c r="L29" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="N29" s="3" t="n">
         <v>37.5</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2407,48 +2407,48 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>54.7</v>
+        <v>58.9</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>128</v>
+        <v>73</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>D-D-U-N</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="L32" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G32" s="3" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>128</v>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>D-D-U-D</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="L32" s="4" t="n">
+      <c r="N32" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="n">
-        <v>36.5</v>
-      </c>
       <c r="O32" s="4" t="n">
-        <v>52</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2590,48 +2590,48 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>46.6</v>
+        <v>38.1</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="G35" s="3" t="n">
-        <v>43.8</v>
+        <v>40.5</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="K35" s="3" t="n">
-        <v>51.7</v>
+        <v>38.1</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N35" s="3" t="n">
-        <v>41.4</v>
+        <v>47.6</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36">
@@ -2764,19 +2764,19 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>42.6</v>
+        <v>43.8</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>68</v>
+        <v>176</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2784,37 +2784,37 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>42.6</v>
+        <v>43.8</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>68</v>
+        <v>176</v>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K38" s="3" t="n">
-        <v>38.5</v>
+        <v>43.4</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N38" s="3" t="n">
-        <v>38.5</v>
+        <v>53.9</v>
       </c>
       <c r="O38" s="4" t="n">
-        <v>26</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3017,25 +3017,25 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>50.6</v>
+        <v>58.5</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>44.7</v>
+        <v>39</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-D</t>
+          <t>U-N-U-U</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>44.8</v>
+        <v>63.9</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>44.8</v>
+        <v>38.9</v>
       </c>
       <c r="O42" s="4" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="43">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3882,14 +3882,14 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>40.5</v>
+        <v>44.4</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="K56" s="3" t="n">
-        <v>75.8</v>
+        <v>63.6</v>
       </c>
       <c r="L56" s="4" t="n">
         <v>33</v>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="N56" s="3" t="n">
-        <v>45.5</v>
+        <v>48.5</v>
       </c>
       <c r="O56" s="4" t="n">
         <v>33</v>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3932,10 +3932,10 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>46.7</v>
+        <v>42.1</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3943,14 +3943,14 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>39.5</v>
+        <v>38.9</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -3959,10 +3959,10 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>43.6</v>
+        <v>35.6</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>43.6</v>
+        <v>42.2</v>
       </c>
       <c r="O57" s="4" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3993,25 +3993,25 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>43.8</v>
+        <v>41.5</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>46.5</v>
+        <v>45.4</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>43.9</v>
+        <v>36.1</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>45.5</v>
+        <v>45.9</v>
       </c>
       <c r="O58" s="4" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59">
@@ -4594,19 +4594,19 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>36.4</v>
+        <v>42.2</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>151</v>
+        <v>90</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4614,14 +4614,14 @@
         </is>
       </c>
       <c r="G68" s="3" t="n">
-        <v>43</v>
+        <v>43.3</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>151</v>
+        <v>90</v>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -4630,10 +4630,10 @@
         </is>
       </c>
       <c r="K68" s="3" t="n">
-        <v>39.6</v>
+        <v>39.1</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
@@ -4641,10 +4641,10 @@
         </is>
       </c>
       <c r="N68" s="3" t="n">
-        <v>50.9</v>
+        <v>43.5</v>
       </c>
       <c r="O68" s="4" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69">
@@ -4838,19 +4838,19 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>51.9</v>
+        <v>36.9</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4858,37 +4858,37 @@
         </is>
       </c>
       <c r="G72" s="3" t="n">
-        <v>37</v>
+        <v>47.5</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K72" s="3" t="n">
-        <v>65</v>
+        <v>45.7</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N72" s="3" t="n">
-        <v>40</v>
+        <v>51.4</v>
       </c>
       <c r="O72" s="4" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="73">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4969,10 +4969,10 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>82</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>172</v>
+        <v>102</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4980,14 +4980,14 @@
         </is>
       </c>
       <c r="G74" s="3" t="n">
-        <v>48.8</v>
+        <v>47.1</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>172</v>
+        <v>102</v>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -4996,10 +4996,10 @@
         </is>
       </c>
       <c r="K74" s="3" t="n">
-        <v>78.3</v>
+        <v>80.8</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
@@ -5007,10 +5007,10 @@
         </is>
       </c>
       <c r="N74" s="3" t="n">
-        <v>52.2</v>
+        <v>57.7</v>
       </c>
       <c r="O74" s="4" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75">
@@ -5021,57 +5021,57 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>38.8</v>
+        <v>39.3</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G75" s="3" t="n">
-        <v>38.8</v>
+        <v>47.4</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K75" s="3" t="n">
-        <v>36.8</v>
+        <v>36.5</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N75" s="3" t="n">
-        <v>42.1</v>
+        <v>46</v>
       </c>
       <c r="O75" s="4" t="n">
-        <v>19</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76">
@@ -5387,19 +5387,19 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>40.2</v>
+        <v>36</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -5407,37 +5407,37 @@
         </is>
       </c>
       <c r="G81" s="3" t="n">
-        <v>44.8</v>
+        <v>45</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>38.6</v>
+        <v>41.9</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="O81" s="4" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="82">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -5457,25 +5457,25 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>77.5</v>
+        <v>56</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="G82" s="3" t="n">
-        <v>46.4</v>
+        <v>36.3</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
@@ -5484,21 +5484,21 @@
         </is>
       </c>
       <c r="K82" s="3" t="n">
-        <v>83.3</v>
+        <v>42.3</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>D/N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N82" s="3" t="n">
-        <v>36.7</v>
+        <v>38.5</v>
       </c>
       <c r="O82" s="4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="83">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -5518,10 +5518,10 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>71.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -5529,14 +5529,14 @@
         </is>
       </c>
       <c r="G83" s="3" t="n">
-        <v>34.8</v>
+        <v>39.7</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c r="K83" s="3" t="n">
-        <v>70.3</v>
+        <v>52.9</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
@@ -5556,10 +5556,10 @@
         </is>
       </c>
       <c r="N83" s="3" t="n">
-        <v>43.2</v>
+        <v>41.2</v>
       </c>
       <c r="O83" s="4" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84">
@@ -5692,57 +5692,57 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>38.3</v>
+        <v>38</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="G86" s="3" t="n">
-        <v>51.9</v>
+        <v>42.2</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="K86" s="3" t="n">
-        <v>44.2</v>
+        <v>45.7</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N86" s="3" t="n">
-        <v>53.5</v>
+        <v>47.1</v>
       </c>
       <c r="O86" s="4" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="87">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>49.4</v>
+        <v>37.8</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5773,14 +5773,14 @@
         </is>
       </c>
       <c r="G87" s="3" t="n">
-        <v>39.8</v>
+        <v>39.6</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
@@ -5789,21 +5789,21 @@
         </is>
       </c>
       <c r="K87" s="3" t="n">
-        <v>43.2</v>
+        <v>42.2</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N87" s="3" t="n">
-        <v>37.8</v>
+        <v>50</v>
       </c>
       <c r="O87" s="4" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="88">
@@ -5814,7 +5814,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5823,10 +5823,10 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>39.4</v>
+        <v>55</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5834,26 +5834,26 @@
         </is>
       </c>
       <c r="G88" s="3" t="n">
-        <v>44.7</v>
+        <v>37</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K88" s="3" t="n">
-        <v>40.3</v>
+        <v>46.5</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
@@ -5861,10 +5861,10 @@
         </is>
       </c>
       <c r="N88" s="3" t="n">
-        <v>50</v>
+        <v>46.5</v>
       </c>
       <c r="O88" s="4" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="89">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -6433,10 +6433,10 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>54.4</v>
+        <v>56.2</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -6444,14 +6444,14 @@
         </is>
       </c>
       <c r="G98" s="3" t="n">
-        <v>40.5</v>
+        <v>43.8</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-U</t>
+          <t>N-N-D-N</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -6460,21 +6460,21 @@
         </is>
       </c>
       <c r="K98" s="3" t="n">
-        <v>59.1</v>
+        <v>69.2</v>
       </c>
       <c r="L98" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="N98" s="3" t="n">
-        <v>36.4</v>
+        <v>42.3</v>
       </c>
       <c r="O98" s="4" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -6494,25 +6494,25 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>63.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G99" s="3" t="n">
-        <v>37.3</v>
+        <v>42.3</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
@@ -6521,21 +6521,21 @@
         </is>
       </c>
       <c r="K99" s="3" t="n">
-        <v>54.5</v>
+        <v>56.8</v>
       </c>
       <c r="L99" s="4" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="N99" s="3" t="n">
-        <v>40.9</v>
+        <v>48.6</v>
       </c>
       <c r="O99" s="4" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>N-U-U</t>
+          <t>N-U-N</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -6730,25 +6730,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>55.6</v>
+        <v>63.6</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>40.7</v>
+        <v>45.5</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-U</t>
+          <t>U-N-U-N</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -6757,21 +6757,21 @@
         </is>
       </c>
       <c r="M2" s="3" t="n">
-        <v>72.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="N2" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P2" s="3" t="n">
-        <v>54.5</v>
+        <v>57.1</v>
       </c>
       <c r="Q2" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>N-N-U</t>
+          <t>N-N-N</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -6801,25 +6801,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>81.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N</t>
         </is>
       </c>
       <c r="I3" s="3" t="n">
-        <v>43.8</v>
+        <v>35.5</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-U</t>
+          <t>U-N-N-N</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -6828,21 +6828,21 @@
         </is>
       </c>
       <c r="M3" s="3" t="n">
-        <v>77.8</v>
+        <v>69.2</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P3" s="3" t="n">
-        <v>55.6</v>
+        <v>53.8</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -7014,48 +7014,48 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M6" s="3" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P6" s="3" t="n">
-        <v>42.9</v>
+        <v>50</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -7156,48 +7156,48 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>43.3</v>
-      </c>
       <c r="J8" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>N-U-U-N</t>
+          <t>N-U-U-U</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M8" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P8" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>50</v>
+        <v>52.6</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -7241,34 +7241,34 @@
         <v>50</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="M9" s="3" t="n">
-        <v>50</v>
+        <v>41.2</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P9" s="3" t="n">
-        <v>60</v>
+        <v>47.1</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -7573,19 +7573,19 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>53.3</v>
+        <v>38.2</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -7593,14 +7593,14 @@
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>46.7</v>
+        <v>44.1</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -7609,10 +7609,10 @@
         </is>
       </c>
       <c r="M14" s="3" t="n">
-        <v>57.1</v>
+        <v>46.2</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="P14" s="3" t="n">
-        <v>42.9</v>
+        <v>61.5</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -7644,57 +7644,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>U-U-U-U</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="n">
         <v>60</v>
       </c>
-      <c r="G15" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>U-U-U-N</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>U</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>100</v>
-      </c>
       <c r="N15" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P15" s="3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>N-D-N</t>
+          <t>N-D-D</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -8008,10 +8008,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -8019,14 +8019,14 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>47.8</v>
+        <v>38.1</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>D-N-D-N</t>
+          <t>D-N-D-D</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -8035,21 +8035,21 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>71.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P20" s="3" t="n">
-        <v>42.9</v>
+        <v>44.4</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -8576,25 +8576,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>57.1</v>
+        <v>61.5</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>57.1</v>
+        <v>46.2</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>D-D-D-N</t>
+          <t>D-D-D-D</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -8603,21 +8603,21 @@
         </is>
       </c>
       <c r="M28" s="3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P28" s="3" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -8647,48 +8647,48 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>57.1</v>
+        <v>55</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>42.9</v>
+        <v>35</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P29" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -8860,25 +8860,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>54.2</v>
+        <v>75</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>45.8</v>
+        <v>56.2</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -8887,21 +8887,21 @@
         </is>
       </c>
       <c r="M32" s="3" t="n">
-        <v>63.6</v>
+        <v>83.3</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P32" s="3" t="n">
-        <v>45.5</v>
+        <v>33.3</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -9073,10 +9073,10 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>60</v>
+        <v>44.8</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -9084,14 +9084,14 @@
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>40</v>
+        <v>51.7</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -9100,10 +9100,10 @@
         </is>
       </c>
       <c r="M35" s="3" t="n">
-        <v>80</v>
+        <v>57.1</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="P35" s="3" t="n">
-        <v>60</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -9277,57 +9277,57 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="I38" s="3" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>D-D-D-D</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="N38" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="I38" s="3" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>D-D-D-N</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="N38" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
       <c r="P38" s="3" t="n">
-        <v>60</v>
+        <v>64.3</v>
       </c>
       <c r="Q38" s="4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>N-U-D</t>
+          <t>N-U-U</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -9570,10 +9570,10 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>45.5</v>
+        <v>70</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -9581,37 +9581,37 @@
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>81.8</v>
+        <v>50</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>U-N-U-D</t>
+          <t>U-N-U-U</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M42" s="3" t="n">
-        <v>66.7</v>
+        <v>80</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="P42" s="3" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Q42" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>D-N-N</t>
+          <t>D-N-D</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>N-D-N-N</t>
+          <t>N-D-N-D</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -10594,18 +10594,18 @@
         <v>100</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P56" s="3" t="n">
-        <v>40</v>
+        <v>66.7</v>
       </c>
       <c r="Q56" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>D-U-U</t>
+          <t>D-U-D</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -10635,34 +10635,34 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>38.7</v>
+        <v>46.9</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>41.9</v>
+        <v>46.9</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-U</t>
+          <t>U-D-U-D</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M57" s="3" t="n">
-        <v>46.2</v>
+        <v>53.8</v>
       </c>
       <c r="N57" s="4" t="n">
         <v>13</v>
@@ -10673,7 +10673,7 @@
         </is>
       </c>
       <c r="P57" s="3" t="n">
-        <v>38.5</v>
+        <v>46.2</v>
       </c>
       <c r="Q57" s="4" t="n">
         <v>13</v>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -10706,48 +10706,48 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>50</v>
+        <v>41.4</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>47.6</v>
+        <v>48.3</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M58" s="3" t="n">
-        <v>45</v>
+        <v>35.3</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P58" s="3" t="n">
-        <v>45</v>
+        <v>52.9</v>
       </c>
       <c r="Q58" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59">
@@ -11407,19 +11407,19 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-N</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>43.2</v>
+        <v>43.8</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
@@ -11427,14 +11427,14 @@
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>48.6</v>
+        <v>37.5</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>D-D-U-D</t>
+          <t>D-D-U-N</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -11443,21 +11443,21 @@
         </is>
       </c>
       <c r="M68" s="3" t="n">
-        <v>43.8</v>
+        <v>66.7</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="P68" s="3" t="n">
-        <v>43.8</v>
+        <v>33.3</v>
       </c>
       <c r="Q68" s="4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -11691,39 +11691,39 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>D-D-N</t>
+          <t>D-D-D</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>42.1</v>
+        <v>44.8</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I72" s="3" t="n">
-        <v>47.4</v>
+        <v>55.2</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>N-D-D-N</t>
+          <t>N-D-D-D</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M72" s="3" t="n">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-U</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -11842,25 +11842,25 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>92.3</v>
+        <v>77.3</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>U-N-N-N</t>
+          <t>U-N-N-U</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -11869,21 +11869,21 @@
         </is>
       </c>
       <c r="M74" s="3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="N74" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="P74" s="3" t="n">
-        <v>63.6</v>
+        <v>40</v>
       </c>
       <c r="Q74" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -11904,46 +11904,46 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>45.5</v>
+        <v>41.7</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>D/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I75" s="3" t="n">
-        <v>36.4</v>
+        <v>50</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="M75" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N75" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -11951,10 +11951,10 @@
         </is>
       </c>
       <c r="P75" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Q75" s="4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>D-U-D</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -12339,10 +12339,10 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>44.2</v>
+        <v>41.2</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
@@ -12350,37 +12350,37 @@
         </is>
       </c>
       <c r="I81" s="3" t="n">
-        <v>46.5</v>
+        <v>50</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-D</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N/U</t>
         </is>
       </c>
       <c r="M81" s="3" t="n">
-        <v>46.2</v>
+        <v>40</v>
       </c>
       <c r="N81" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P81" s="3" t="n">
-        <v>53.8</v>
+        <v>46.7</v>
       </c>
       <c r="Q81" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="82">
@@ -12401,7 +12401,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>N-N-N</t>
+          <t>N-N-D</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -12410,37 +12410,37 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>77.8</v>
+        <v>66.7</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>44.4</v>
+        <v>42.9</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>D-N-N-N</t>
+          <t>D-N-N-D</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/N/U</t>
         </is>
       </c>
       <c r="M82" s="3" t="n">
-        <v>100</v>
+        <v>33.3</v>
       </c>
       <c r="N82" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -12448,10 +12448,10 @@
         </is>
       </c>
       <c r="P82" s="3" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Q82" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>D-N-U</t>
+          <t>D-N-N</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -12481,48 +12481,48 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>76.2</v>
+        <v>75</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I83" s="3" t="n">
-        <v>47.6</v>
+        <v>41.7</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>D-D-N-U</t>
+          <t>D-D-N-N</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M83" s="3" t="n">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="N83" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="P83" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q83" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -12685,57 +12685,57 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>D-U-N</t>
+          <t>D-U-U</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>55.6</v>
+        <v>45.2</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>66.7</v>
+        <v>41.9</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>U-D-U-N</t>
+          <t>U-D-U-U</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="M86" s="3" t="n">
-        <v>55.6</v>
+        <v>46.7</v>
       </c>
       <c r="N86" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P86" s="3" t="n">
-        <v>66.7</v>
+        <v>46.7</v>
       </c>
       <c r="Q86" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -12765,10 +12765,10 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>42.9</v>
+        <v>47.1</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
@@ -12776,37 +12776,37 @@
         </is>
       </c>
       <c r="I87" s="3" t="n">
-        <v>42.9</v>
+        <v>52.9</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M87" s="3" t="n">
-        <v>37.5</v>
+        <v>64.3</v>
       </c>
       <c r="N87" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P87" s="3" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="Q87" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="88">
@@ -12827,34 +12827,34 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>U-U-D</t>
+          <t>U-U-N</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>43.3</v>
+        <v>48</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>D/U</t>
         </is>
       </c>
       <c r="I88" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>D-U-U-D</t>
+          <t>D-U-U-N</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -12863,10 +12863,10 @@
         </is>
       </c>
       <c r="M88" s="3" t="n">
-        <v>52.6</v>
+        <v>60</v>
       </c>
       <c r="N88" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -12874,10 +12874,10 @@
         </is>
       </c>
       <c r="P88" s="3" t="n">
-        <v>47.4</v>
+        <v>60</v>
       </c>
       <c r="Q88" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="89">
@@ -13537,57 +13537,57 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>N-D-U</t>
+          <t>N-D-N</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="I98" s="3" t="n">
-        <v>40</v>
+        <v>41.7</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>N-N-D-U</t>
+          <t>N-N-D-N</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M98" s="3" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="N98" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>N/U</t>
+          <t>U</t>
         </is>
       </c>
       <c r="P98" s="3" t="n">
         <v>50</v>
       </c>
       <c r="Q98" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
@@ -13608,7 +13608,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>U-U-N</t>
+          <t>U-U-U</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -13617,25 +13617,25 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>62.9</v>
+        <v>53.3</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>U</t>
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>37.1</v>
+        <v>60</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>U-U-U-N</t>
+          <t>U-U-U-U</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
@@ -13644,21 +13644,21 @@
         </is>
       </c>
       <c r="M99" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="N99" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="P99" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="N99" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="O99" s="2" t="inlineStr">
-        <is>
-          <t>D/N</t>
-        </is>
-      </c>
-      <c r="P99" s="3" t="n">
-        <v>40</v>
-      </c>
       <c r="Q99" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
